--- a/data/orders/2026-T3_declaration_tps_tvq.xlsx
+++ b/data/orders/2026-T3_declaration_tps_tvq.xlsx
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>6446.89</v>
+        <v>10499.66</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>322.34</v>
+        <v>524.98</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>643.08</v>
+        <v>1047.34</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="D12" s="12" t="n">
-        <v>5887.99</v>
+        <v>9596.16</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>298.79</v>
+        <v>485.67</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>591.78</v>
+        <v>964.64</v>
       </c>
     </row>
     <row r="14">

--- a/data/orders/2026-T3_declaration_tps_tvq.xlsx
+++ b/data/orders/2026-T3_declaration_tps_tvq.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Déclaration TPS-TVQ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dépenses" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="0.000%"/>
     <numFmt numFmtId="165" formatCode="#,##0.00 &quot;$&quot;"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,8 +67,30 @@
       <color rgb="FF595959"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFC00000"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -104,6 +127,16 @@
         <fgColor rgb="FFEEF4FB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9E7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -131,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -174,6 +207,24 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -537,9 +588,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F15"/>
+  <dimension ref="B2:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -685,11 +736,288 @@
         </is>
       </c>
     </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>SECTION B — DÉPENSES (taxes payées sur les achats et frais)</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Montant HT ($)</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>TPS payée ($)</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>TVQ payée ($)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>CTI / RTI</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Dépenses (0 pièce)</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Aucune dépense : déposer les factures et reçus dans le dossier depenses/2026-T3/ du dépôt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>SECTION C — SOLDE À PAYER OU À RÉCLAMER</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="B23" s="10" t="inlineStr"/>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>TPS ($)</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>TVQ ($)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="14" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Taxes perçues des clients (Shopify, ligne 105/205)</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="13" t="n">
+        <v>485.67</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>964.64</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="14" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Moins : taxes payées sur les dépenses</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="B26" s="16" t="inlineStr"/>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>Taxe nette (perçue − payée)</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="18" t="n">
+        <v>485.67</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>964.64</v>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>TPS : 485,67 $ à payer à Revenu Québec</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="n"/>
+      <c r="F28" s="20" t="n"/>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>TVQ : 964,64 $ à payer à Revenu Québec</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="20" t="n"/>
+      <c r="E29" s="20" t="n"/>
+      <c r="F29" s="20" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="9">
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="B28:F28"/>
     <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C26:D26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>Fichier</t>
+        </is>
+      </c>
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="21" t="inlineStr">
+        <is>
+          <t>Fournisseur</t>
+        </is>
+      </c>
+      <c r="D1" s="21" t="inlineStr">
+        <is>
+          <t>N° facture</t>
+        </is>
+      </c>
+      <c r="E1" s="21" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F1" s="21" t="inlineStr">
+        <is>
+          <t>Montant HT ($)</t>
+        </is>
+      </c>
+      <c r="G1" s="21" t="inlineStr">
+        <is>
+          <t>TPS payée ($)</t>
+        </is>
+      </c>
+      <c r="H1" s="21" t="inlineStr">
+        <is>
+          <t>TVQ payée ($)</t>
+        </is>
+      </c>
+      <c r="I1" s="21" t="inlineStr">
+        <is>
+          <t>Total ($)</t>
+        </is>
+      </c>
+      <c r="J1" s="21" t="inlineStr">
+        <is>
+          <t>Lu par</t>
+        </is>
+      </c>
+      <c r="K1" s="21" t="inlineStr">
+        <is>
+          <t>Remarques</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="n"/>
+      <c r="C2" s="22" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="22" t="n"/>
+      <c r="F2" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="22" t="n"/>
+      <c r="J2" s="22" t="n"/>
+      <c r="K2" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/data/orders/2026-T3_declaration_tps_tvq.xlsx
+++ b/data/orders/2026-T3_declaration_tps_tvq.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="0.000%"/>
     <numFmt numFmtId="165" formatCode="#,##0.00 &quot;$&quot;"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,6 +77,12 @@
       <b val="1"/>
       <color rgb="FFC00000"/>
       <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -164,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -220,11 +226,14 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="11" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="12" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -590,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F29"/>
+  <dimension ref="B2:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -896,6 +905,34 @@
       <c r="D29" s="20" t="n"/>
       <c r="E29" s="20" t="n"/>
       <c r="F29" s="20" t="n"/>
+    </row>
+    <row r="31">
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>ATTENTION — 2026-T3/IMG_2959.jpeg : erreur de lecture (API Anthropic 400 : {"type":"error","error":{"type":"invalid_request_error","message":"tool_choice: type \"tool\" and \"any\" are not supported for this model."},"request_id":"req_011Cg3H7GFATNp6gMMMuJTDi"}), document non compté</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>ATTENTION — 2026-T3/IMG_2962.jpeg : erreur de lecture (API Anthropic 400 : {"type":"error","error":{"type":"invalid_request_error","message":"tool_choice: type \"tool\" and \"any\" are not supported for this model."},"request_id":"req_011Cg3H7KuBsyZtQWe5g9Bkx"}), document non compté</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>ATTENTION — 2026-T3/IMG_2963.jpeg : erreur de lecture (API Anthropic 400 : {"type":"error","error":{"type":"invalid_request_error","message":"tool_choice: type \"tool\" and \"any\" are not supported for this model."},"request_id":"req_011Cg3H7MC4r1UrZ6mR86TC6"}), document non compté</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>ATTENTION — 2026-T3/IMG_2964.jpeg : erreur de lecture (API Anthropic 400 : {"type":"error","error":{"type":"invalid_request_error","message":"tool_choice: type \"tool\" and \"any\" are not supported for this model."},"request_id":"req_011Cg3H7PmLrHM6NefMDgWki"}), document non compté</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -937,84 +974,84 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Fichier</t>
         </is>
       </c>
-      <c r="B1" s="21" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="21" t="inlineStr">
+      <c r="C1" s="22" t="inlineStr">
         <is>
           <t>Fournisseur</t>
         </is>
       </c>
-      <c r="D1" s="21" t="inlineStr">
+      <c r="D1" s="22" t="inlineStr">
         <is>
           <t>N° facture</t>
         </is>
       </c>
-      <c r="E1" s="21" t="inlineStr">
+      <c r="E1" s="22" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="F1" s="21" t="inlineStr">
+      <c r="F1" s="22" t="inlineStr">
         <is>
           <t>Montant HT ($)</t>
         </is>
       </c>
-      <c r="G1" s="21" t="inlineStr">
+      <c r="G1" s="22" t="inlineStr">
         <is>
           <t>TPS payée ($)</t>
         </is>
       </c>
-      <c r="H1" s="21" t="inlineStr">
+      <c r="H1" s="22" t="inlineStr">
         <is>
           <t>TVQ payée ($)</t>
         </is>
       </c>
-      <c r="I1" s="21" t="inlineStr">
+      <c r="I1" s="22" t="inlineStr">
         <is>
           <t>Total ($)</t>
         </is>
       </c>
-      <c r="J1" s="21" t="inlineStr">
+      <c r="J1" s="22" t="inlineStr">
         <is>
           <t>Lu par</t>
         </is>
       </c>
-      <c r="K1" s="21" t="inlineStr">
+      <c r="K1" s="22" t="inlineStr">
         <is>
           <t>Remarques</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B2" s="22" t="n"/>
-      <c r="C2" s="22" t="n"/>
-      <c r="D2" s="22" t="n"/>
-      <c r="E2" s="22" t="n"/>
-      <c r="F2" s="23" t="n">
+      <c r="B2" s="23" t="n"/>
+      <c r="C2" s="23" t="n"/>
+      <c r="D2" s="23" t="n"/>
+      <c r="E2" s="23" t="n"/>
+      <c r="F2" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="23" t="n">
+      <c r="G2" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="23" t="n">
+      <c r="H2" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="22" t="n"/>
-      <c r="J2" s="22" t="n"/>
-      <c r="K2" s="22" t="n"/>
+      <c r="I2" s="23" t="n"/>
+      <c r="J2" s="23" t="n"/>
+      <c r="K2" s="23" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/orders/2026-T3_declaration_tps_tvq.xlsx
+++ b/data/orders/2026-T3_declaration_tps_tvq.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="0.000%"/>
     <numFmt numFmtId="165" formatCode="#,##0.00 &quot;$&quot;"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,6 +89,15 @@
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FFC00000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -170,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -232,8 +241,11 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="12" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="14" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -599,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F34"/>
+  <dimension ref="B2:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -790,23 +802,23 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Dépenses (0 pièce)</t>
+          <t>Dépenses (3 pièces)</t>
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0</v>
+        <v>608.99</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>0</v>
+        <v>30.45</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0</v>
+        <v>60.75</v>
       </c>
     </row>
     <row r="20">
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>Aucune dépense : déposer les factures et reçus dans le dossier depenses/2026-T3/ du dépôt.</t>
+          <t>Détail ligne par ligne dans l'onglet « Dépenses ».</t>
         </is>
       </c>
     </row>
@@ -863,10 +875,10 @@
       </c>
       <c r="D25" s="14" t="n"/>
       <c r="E25" s="13" t="n">
-        <v>-0</v>
+        <v>-30.45</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>-0</v>
+        <v>-60.75</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -878,16 +890,16 @@
       </c>
       <c r="D26" s="16" t="n"/>
       <c r="E26" s="18" t="n">
-        <v>485.67</v>
+        <v>455.22</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>964.64</v>
+        <v>903.89</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>TPS : 485,67 $ à payer à Revenu Québec</t>
+          <t>TPS : 455,22 $ à payer à Revenu Québec</t>
         </is>
       </c>
       <c r="C28" s="20" t="n"/>
@@ -898,7 +910,7 @@
     <row r="29" ht="24" customHeight="1">
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>TVQ : 964,64 $ à payer à Revenu Québec</t>
+          <t>TVQ : 903,89 $ à payer à Revenu Québec</t>
         </is>
       </c>
       <c r="C29" s="20" t="n"/>
@@ -909,28 +921,7 @@
     <row r="31">
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>ATTENTION — 2026-T3/IMG_2959.jpeg : erreur de lecture (API Anthropic 400 : {"type":"error","error":{"type":"invalid_request_error","message":"tool_choice: type \"tool\" and \"any\" are not supported for this model."},"request_id":"req_011Cg3H7GFATNp6gMMMuJTDi"}), document non compté</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" s="21" t="inlineStr">
-        <is>
-          <t>ATTENTION — 2026-T3/IMG_2962.jpeg : erreur de lecture (API Anthropic 400 : {"type":"error","error":{"type":"invalid_request_error","message":"tool_choice: type \"tool\" and \"any\" are not supported for this model."},"request_id":"req_011Cg3H7KuBsyZtQWe5g9Bkx"}), document non compté</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" s="21" t="inlineStr">
-        <is>
-          <t>ATTENTION — 2026-T3/IMG_2963.jpeg : erreur de lecture (API Anthropic 400 : {"type":"error","error":{"type":"invalid_request_error","message":"tool_choice: type \"tool\" and \"any\" are not supported for this model."},"request_id":"req_011Cg3H7MC4r1UrZ6mR86TC6"}), document non compté</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" s="21" t="inlineStr">
-        <is>
-          <t>ATTENTION — 2026-T3/IMG_2964.jpeg : erreur de lecture (API Anthropic 400 : {"type":"error","error":{"type":"invalid_request_error","message":"tool_choice: type \"tool\" and \"any\" are not supported for this model."},"request_id":"req_011Cg3H7PmLrHM6NefMDgWki"}), document non compté</t>
+          <t>ATTENTION — Doublon exclu : La perle virtuelle du 2026-07-08 (facture 26005) se trouve dans 2026-T3/IMG_2959.jpeg et 2026-T3/IMG_2963.jpeg : comptée une seule fois</t>
         </is>
       </c>
     </row>
@@ -957,7 +948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1033,25 +1024,170 @@
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B2" s="23" t="n"/>
-      <c r="C2" s="23" t="n"/>
-      <c r="D2" s="23" t="n"/>
-      <c r="E2" s="23" t="n"/>
-      <c r="F2" s="24" t="n">
-        <v>0</v>
-      </c>
+          <t>2026-T3/IMG_2964.jpeg</t>
+        </is>
+      </c>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C2" s="23" t="inlineStr">
+        <is>
+          <t>DHL Express</t>
+        </is>
+      </c>
+      <c r="D2" s="23" t="inlineStr">
+        <is>
+          <t>204557218-108434242</t>
+        </is>
+      </c>
+      <c r="E2" s="23" t="inlineStr">
+        <is>
+          <t>Envoi DHL Express (bordereau 3157487874), expéditeur Miss Pretty Lashes</t>
+        </is>
+      </c>
+      <c r="F2" s="24" t="n"/>
       <c r="G2" s="24" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="23" t="n"/>
-      <c r="J2" s="23" t="n"/>
-      <c r="K2" s="23" t="n"/>
+      <c r="I2" s="24" t="n">
+        <v>40.31</v>
+      </c>
+      <c r="J2" s="23" t="inlineStr">
+        <is>
+          <t>photo (lue par IA)</t>
+        </is>
+      </c>
+      <c r="K2" s="25" t="inlineStr">
+        <is>
+          <t>Confirmation de paiement (même document en français et en anglais, comptée une seule fois). Aucune taxe imprimée ; montant HT non indiqué. Les annotations manuscrites (TVQ, TPS) ont été ignorées. Numéro de facture = ID de transaction. ; Date 2026-06-24 hors du trimestre 2026-T3</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/IMG_2959.jpeg</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C3" s="23" t="inlineStr">
+        <is>
+          <t>La perle virtuelle</t>
+        </is>
+      </c>
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t>26005</t>
+        </is>
+      </c>
+      <c r="E3" s="23" t="inlineStr">
+        <is>
+          <t>Journée de contenu - Présentiel (soutien technique et administratif, création de contenu, gestion de projet, stratégies) le 6 juillet 2026</t>
+        </is>
+      </c>
+      <c r="F3" s="24" t="n">
+        <v>595</v>
+      </c>
+      <c r="G3" s="24" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="H3" s="24" t="n">
+        <v>59.35</v>
+      </c>
+      <c r="I3" s="24" t="n">
+        <v>684.1</v>
+      </c>
+      <c r="J3" s="23" t="inlineStr">
+        <is>
+          <t>photo (lue par IA)</t>
+        </is>
+      </c>
+      <c r="K3" s="25" t="inlineStr">
+        <is>
+          <t>Vérification : 595,00 + 29,75 + 59,35 = 684,10. Les annotations manuscrites ont été ignorées.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/IMG_2962.jpeg</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>Canadian Tire #928</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>TRANS: 139</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>GLD BLEU P50 45 (article de quincaillerie/fournitures)</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="G4" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H4" s="24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I4" s="24" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="J4" s="23" t="inlineStr">
+        <is>
+          <t>photo (lue par IA)</t>
+        </is>
+      </c>
+      <c r="K4" s="25" t="inlineStr">
+        <is>
+          <t>Annotation manuscrite ignorée. Le numéro de facture est le numéro de transaction (TRANS 139). La TVQ imprimée est de 1,40 $, ce qui correspond à 9,975 % de 13,99 $ (1,395 arrondi).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="27" t="n">
+        <v>608.99</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>30.45</v>
+      </c>
+      <c r="H5" s="27" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="I5" s="26" t="n"/>
+      <c r="J5" s="26" t="n"/>
+      <c r="K5" s="26" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/orders/2026-T3_declaration_tps_tvq.xlsx
+++ b/data/orders/2026-T3_declaration_tps_tvq.xlsx
@@ -611,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F31"/>
+  <dimension ref="B2:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -920,6 +920,20 @@
     </row>
     <row r="31">
       <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>ATTENTION — 2026-T3/Dépenses_T3-1-20.pdf : aucune dépense avec taxes trouvée</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>ATTENTION — 2026-T3/Dépenses_T3-21-39.pdf : aucune dépense avec taxes trouvée</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>ATTENTION — Doublon exclu : La perle virtuelle du 2026-07-08 (facture 26005) se trouve dans 2026-T3/IMG_2959.jpeg et 2026-T3/IMG_2963.jpeg : comptée une seule fois</t>
         </is>
@@ -948,20 +962,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -982,40 +997,45 @@
       </c>
       <c r="D1" s="22" t="inlineStr">
         <is>
+          <t>Catégorie</t>
+        </is>
+      </c>
+      <c r="E1" s="22" t="inlineStr">
+        <is>
           <t>N° facture</t>
         </is>
       </c>
-      <c r="E1" s="22" t="inlineStr">
+      <c r="F1" s="22" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="F1" s="22" t="inlineStr">
+      <c r="G1" s="22" t="inlineStr">
         <is>
           <t>Montant HT ($)</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="H1" s="22" t="inlineStr">
         <is>
           <t>TPS payée ($)</t>
         </is>
       </c>
-      <c r="H1" s="22" t="inlineStr">
+      <c r="I1" s="22" t="inlineStr">
         <is>
           <t>TVQ payée ($)</t>
         </is>
       </c>
-      <c r="I1" s="22" t="inlineStr">
+      <c r="J1" s="22" t="inlineStr">
         <is>
           <t>Total ($)</t>
         </is>
       </c>
-      <c r="J1" s="22" t="inlineStr">
+      <c r="K1" s="22" t="inlineStr">
         <is>
           <t>Lu par</t>
         </is>
       </c>
-      <c r="K1" s="22" t="inlineStr">
+      <c r="L1" s="22" t="inlineStr">
         <is>
           <t>Remarques</t>
         </is>
@@ -1039,32 +1059,37 @@
       </c>
       <c r="D2" s="23" t="inlineStr">
         <is>
+          <t>Frais de livraison</t>
+        </is>
+      </c>
+      <c r="E2" s="23" t="inlineStr">
+        <is>
           <t>204557218-108434242</t>
         </is>
       </c>
-      <c r="E2" s="23" t="inlineStr">
-        <is>
-          <t>Envoi DHL Express (bordereau 3157487874), expéditeur Miss Pretty Lashes</t>
-        </is>
-      </c>
-      <c r="F2" s="24" t="n"/>
-      <c r="G2" s="24" t="n">
-        <v>0</v>
-      </c>
+      <c r="F2" s="23" t="inlineStr">
+        <is>
+          <t>Envoi DHL Express (waybill 3157487874) - confirmation de paiement</t>
+        </is>
+      </c>
+      <c r="G2" s="24" t="n"/>
       <c r="H2" s="24" t="n">
         <v>0</v>
       </c>
       <c r="I2" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="24" t="n">
         <v>40.31</v>
       </c>
-      <c r="J2" s="23" t="inlineStr">
+      <c r="K2" s="23" t="inlineStr">
         <is>
           <t>photo (lue par IA)</t>
         </is>
       </c>
-      <c r="K2" s="25" t="inlineStr">
-        <is>
-          <t>Confirmation de paiement (même document en français et en anglais, comptée une seule fois). Aucune taxe imprimée ; montant HT non indiqué. Les annotations manuscrites (TVQ, TPS) ont été ignorées. Numéro de facture = ID de transaction. ; Date 2026-06-24 hors du trimestre 2026-T3</t>
+      <c r="L2" s="25" t="inlineStr">
+        <is>
+          <t>Confirmation de paiement seulement : aucun montant de TPS/TVQ imprimé ni mention de taxes incluses. Numéro indiqué = ID de transaction. Annotations manuscrites (TVQ, TPS) ignorées. Le document apparaît deux fois (version française et anglaise) : une seule dépense. ; Date 2026-06-24 hors du trimestre 2026-T3</t>
         </is>
       </c>
     </row>
@@ -1086,34 +1111,39 @@
       </c>
       <c r="D3" s="23" t="inlineStr">
         <is>
+          <t>Soutien technique</t>
+        </is>
+      </c>
+      <c r="E3" s="23" t="inlineStr">
+        <is>
           <t>26005</t>
         </is>
       </c>
-      <c r="E3" s="23" t="inlineStr">
-        <is>
-          <t>Journée de contenu - Présentiel (soutien technique et administratif, création de contenu, gestion de projet, stratégies) le 6 juillet 2026</t>
-        </is>
-      </c>
-      <c r="F3" s="24" t="n">
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t>Journée de contenu - Présentiel (soutien technique et administratif, création de contenu, gestion de projet, stratégies) le 06 juillet 2026</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="n">
         <v>595</v>
       </c>
-      <c r="G3" s="24" t="n">
+      <c r="H3" s="24" t="n">
         <v>29.75</v>
       </c>
-      <c r="H3" s="24" t="n">
+      <c r="I3" s="24" t="n">
         <v>59.35</v>
       </c>
-      <c r="I3" s="24" t="n">
+      <c r="J3" s="24" t="n">
         <v>684.1</v>
       </c>
-      <c r="J3" s="23" t="inlineStr">
+      <c r="K3" s="23" t="inlineStr">
         <is>
           <t>photo (lue par IA)</t>
         </is>
       </c>
-      <c r="K3" s="25" t="inlineStr">
-        <is>
-          <t>Vérification : 595,00 + 29,75 + 59,35 = 684,10. Les annotations manuscrites ont été ignorées.</t>
+      <c r="L3" s="25" t="inlineStr">
+        <is>
+          <t>Le sous-total de 595,00 $ plus TPS de 29,75 $ et TVQ de 59,35 $ donne 684,10 $, ce qui correspond au grand total. Les annotations manuscrites ont été ignorées.</t>
         </is>
       </c>
     </row>
@@ -1135,34 +1165,39 @@
       </c>
       <c r="D4" s="23" t="inlineStr">
         <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
           <t>TRANS: 139</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
-        <is>
-          <t>GLD BLEU P50 45 (article de quincaillerie/fournitures)</t>
-        </is>
-      </c>
-      <c r="F4" s="24" t="n">
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>GLD BLEU P50 45 (article 142-4701-0)</t>
+        </is>
+      </c>
+      <c r="G4" s="24" t="n">
         <v>13.99</v>
       </c>
-      <c r="G4" s="24" t="n">
+      <c r="H4" s="24" t="n">
         <v>0.7</v>
       </c>
-      <c r="H4" s="24" t="n">
+      <c r="I4" s="24" t="n">
         <v>1.4</v>
       </c>
-      <c r="I4" s="24" t="n">
+      <c r="J4" s="24" t="n">
         <v>16.09</v>
       </c>
-      <c r="J4" s="23" t="inlineStr">
+      <c r="K4" s="23" t="inlineStr">
         <is>
           <t>photo (lue par IA)</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
-        <is>
-          <t>Annotation manuscrite ignorée. Le numéro de facture est le numéro de transaction (TRANS 139). La TVQ imprimée est de 1,40 $, ce qui correspond à 9,975 % de 13,99 $ (1,395 arrondi).</t>
+      <c r="L4" s="25" t="inlineStr">
+        <is>
+          <t>Annotation manuscrite ignorée. Payé par Mastercard. Le numéro de transaction est utilisé comme numéro de reçu.</t>
         </is>
       </c>
     </row>
@@ -1176,18 +1211,19 @@
       <c r="C5" s="26" t="n"/>
       <c r="D5" s="26" t="n"/>
       <c r="E5" s="26" t="n"/>
-      <c r="F5" s="27" t="n">
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="27" t="n">
         <v>608.99</v>
       </c>
-      <c r="G5" s="27" t="n">
+      <c r="H5" s="27" t="n">
         <v>30.45</v>
       </c>
-      <c r="H5" s="27" t="n">
+      <c r="I5" s="27" t="n">
         <v>60.75</v>
       </c>
-      <c r="I5" s="26" t="n"/>
       <c r="J5" s="26" t="n"/>
       <c r="K5" s="26" t="n"/>
+      <c r="L5" s="26" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/orders/2026-T3_declaration_tps_tvq.xlsx
+++ b/data/orders/2026-T3_declaration_tps_tvq.xlsx
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>608.99</v>
+        <v>644.05</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>30.45</v>
+        <v>32.2</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>60.75</v>
+        <v>64.25</v>
       </c>
     </row>
     <row r="20">
@@ -875,10 +875,10 @@
       </c>
       <c r="D25" s="14" t="n"/>
       <c r="E25" s="13" t="n">
-        <v>-30.45</v>
+        <v>-32.2</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>-60.75</v>
+        <v>-64.25</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -890,16 +890,16 @@
       </c>
       <c r="D26" s="16" t="n"/>
       <c r="E26" s="18" t="n">
-        <v>455.22</v>
+        <v>453.47</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>903.89</v>
+        <v>900.39</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>TPS : 455,22 $ à payer à Revenu Québec</t>
+          <t>TPS : 453,47 $ à payer à Revenu Québec</t>
         </is>
       </c>
       <c r="C28" s="20" t="n"/>
@@ -910,7 +910,7 @@
     <row r="29" ht="24" customHeight="1">
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>TVQ : 903,89 $ à payer à Revenu Québec</t>
+          <t>TVQ : 900,39 $ à payer à Revenu Québec</t>
         </is>
       </c>
       <c r="C29" s="20" t="n"/>
@@ -1069,27 +1069,29 @@
       </c>
       <c r="F2" s="23" t="inlineStr">
         <is>
-          <t>Envoi DHL Express (waybill 3157487874) - confirmation de paiement</t>
-        </is>
-      </c>
-      <c r="G2" s="24" t="n"/>
+          <t>Envoi DHL Express (bordereau 3157487874) – Miss Pretty Lashes</t>
+        </is>
+      </c>
+      <c r="G2" s="24" t="n">
+        <v>35.06</v>
+      </c>
       <c r="H2" s="24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="I2" s="24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J2" s="24" t="n">
         <v>40.31</v>
       </c>
       <c r="K2" s="23" t="inlineStr">
         <is>
-          <t>photo (lue par IA)</t>
+          <t>photo (lue par IA), taxes calculées</t>
         </is>
       </c>
       <c r="L2" s="25" t="inlineStr">
         <is>
-          <t>Confirmation de paiement seulement : aucun montant de TPS/TVQ imprimé ni mention de taxes incluses. Numéro indiqué = ID de transaction. Annotations manuscrites (TVQ, TPS) ignorées. Le document apparaît deux fois (version française et anglaise) : une seule dépense. ; Date 2026-06-24 hors du trimestre 2026-T3</t>
+          <t>Confirmation de paiement en français et en anglais (même transaction, comptée une seule fois). Aucun montant de taxe imprimé; les annotations manuscrites (TVQ, TPS) sont ignorées. Le numéro de facture est l'ID de transaction. ; TPS/TVQ calculées à partir du total taxes incluses (40.31 $ = 35.06 HT + 1.75 TPS 5 % + 3.50 TVQ 9,975 %) ; Date 2026-06-24 hors du trimestre 2026-T3</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1123,7 @@
       </c>
       <c r="F3" s="23" t="inlineStr">
         <is>
-          <t>Journée de contenu - Présentiel (soutien technique et administratif, création de contenu, gestion de projet, stratégies) le 06 juillet 2026</t>
+          <t>Journée de contenu - Présentiel (soutien technique et administratif, création de contenu, gestion de projet)</t>
         </is>
       </c>
       <c r="G3" s="24" t="n">
@@ -1141,11 +1143,7 @@
           <t>photo (lue par IA)</t>
         </is>
       </c>
-      <c r="L3" s="25" t="inlineStr">
-        <is>
-          <t>Le sous-total de 595,00 $ plus TPS de 29,75 $ et TVQ de 59,35 $ donne 684,10 $, ce qui correspond au grand total. Les annotations manuscrites ont été ignorées.</t>
-        </is>
-      </c>
+      <c r="L3" s="23" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="23" t="inlineStr">
@@ -1175,7 +1173,7 @@
       </c>
       <c r="F4" s="23" t="inlineStr">
         <is>
-          <t>GLD BLEU P50 45 (article 142-4701-0)</t>
+          <t>GLD BLEU P50 45 (article de quincaillerie/papeterie)</t>
         </is>
       </c>
       <c r="G4" s="24" t="n">
@@ -1197,7 +1195,7 @@
       </c>
       <c r="L4" s="25" t="inlineStr">
         <is>
-          <t>Annotation manuscrite ignorée. Payé par Mastercard. Le numéro de transaction est utilisé comme numéro de reçu.</t>
+          <t>Payé par Mastercard ****6337. Annotation manuscrite ignorée.</t>
         </is>
       </c>
     </row>
@@ -1213,13 +1211,13 @@
       <c r="E5" s="26" t="n"/>
       <c r="F5" s="26" t="n"/>
       <c r="G5" s="27" t="n">
-        <v>608.99</v>
+        <v>644.05</v>
       </c>
       <c r="H5" s="27" t="n">
-        <v>30.45</v>
+        <v>32.2</v>
       </c>
       <c r="I5" s="27" t="n">
-        <v>60.75</v>
+        <v>64.25</v>
       </c>
       <c r="J5" s="26" t="n"/>
       <c r="K5" s="26" t="n"/>

--- a/data/orders/2026-T3_declaration_tps_tvq.xlsx
+++ b/data/orders/2026-T3_declaration_tps_tvq.xlsx
@@ -1069,7 +1069,7 @@
       </c>
       <c r="F2" s="23" t="inlineStr">
         <is>
-          <t>Envoi DHL Express (bordereau 3157487874) – Miss Pretty Lashes</t>
+          <t>Envoi DHL Express (bordereau 3157487874) - Miss Pretty Lashes</t>
         </is>
       </c>
       <c r="G2" s="24" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="L2" s="25" t="inlineStr">
         <is>
-          <t>Confirmation de paiement en français et en anglais (même transaction, comptée une seule fois). Aucun montant de taxe imprimé; les annotations manuscrites (TVQ, TPS) sont ignorées. Le numéro de facture est l'ID de transaction. ; TPS/TVQ calculées à partir du total taxes incluses (40.31 $ = 35.06 HT + 1.75 TPS 5 % + 3.50 TVQ 9,975 %) ; Date 2026-06-24 hors du trimestre 2026-T3</t>
+          <t>Confirmation de paiement en français et en anglais (même transaction, comptée une seule fois). Aucun montant de taxe imprimé. Annotations manuscrites TVQ/TPS ignorées (sans « ? »). Numéro de facture = ID de transaction. ; TPS/TVQ calculées à partir du total taxes incluses (40.31 $ = 35.06 HT + 1.75 TPS 5 % + 3.50 TVQ 9,975 %) ; Date 2026-06-24 hors du trimestre 2026-T3</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="E4" s="23" t="inlineStr">
         <is>
-          <t>TRANS: 139</t>
+          <t>TRANS 139</t>
         </is>
       </c>
       <c r="F4" s="23" t="inlineStr">
         <is>
-          <t>GLD BLEU P50 45 (article de quincaillerie/papeterie)</t>
+          <t>GLD BLEU P50 45 (article de quincaillerie)</t>
         </is>
       </c>
       <c r="G4" s="24" t="n">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="L4" s="25" t="inlineStr">
         <is>
-          <t>Payé par Mastercard ****6337. Annotation manuscrite ignorée.</t>
+          <t>Date imprimée 08/25/2026; annotation manuscrite « oct 2026 » ignorée. TVQ imprimée 1,40 (9,975 % de 13,99 = 1,395).</t>
         </is>
       </c>
     </row>

--- a/data/orders/2026-T3_declaration_tps_tvq.xlsx
+++ b/data/orders/2026-T3_declaration_tps_tvq.xlsx
@@ -611,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F33"/>
+  <dimension ref="B2:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -802,17 +802,17 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Dépenses (3 pièces)</t>
+          <t>Dépenses (42 pièces)</t>
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>644.05</v>
+        <v>5577.05</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>32.2</v>
+        <v>303.61</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>64.25</v>
+        <v>538.1799999999999</v>
       </c>
     </row>
     <row r="20">
@@ -875,10 +875,10 @@
       </c>
       <c r="D25" s="14" t="n"/>
       <c r="E25" s="13" t="n">
-        <v>-32.2</v>
+        <v>-303.61</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>-64.25</v>
+        <v>-538.1799999999999</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -890,16 +890,16 @@
       </c>
       <c r="D26" s="16" t="n"/>
       <c r="E26" s="18" t="n">
-        <v>453.47</v>
+        <v>182.06</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>900.39</v>
+        <v>426.46</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>TPS : 453,47 $ à payer à Revenu Québec</t>
+          <t>TPS : 182,06 $ à payer à Revenu Québec</t>
         </is>
       </c>
       <c r="C28" s="20" t="n"/>
@@ -910,7 +910,7 @@
     <row r="29" ht="24" customHeight="1">
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>TVQ : 900,39 $ à payer à Revenu Québec</t>
+          <t>TVQ : 426,46 $ à payer à Revenu Québec</t>
         </is>
       </c>
       <c r="C29" s="20" t="n"/>
@@ -920,20 +920,6 @@
     </row>
     <row r="31">
       <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>ATTENTION — 2026-T3/Dépenses_T3-1-20.pdf : aucune dépense avec taxes trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" s="21" t="inlineStr">
-        <is>
-          <t>ATTENTION — 2026-T3/Dépenses_T3-21-39.pdf : aucune dépense avec taxes trouvée</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>ATTENTION — Doublon exclu : La perle virtuelle du 2026-07-08 (facture 26005) se trouve dans 2026-T3/IMG_2959.jpeg et 2026-T3/IMG_2963.jpeg : comptée une seule fois</t>
         </is>
@@ -962,7 +948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1044,184 +1030,2198 @@
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>2026-T3/IMG_2964.jpeg</t>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
         </is>
       </c>
       <c r="B2" s="23" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="C2" s="23" t="inlineStr">
         <is>
-          <t>DHL Express</t>
+          <t>H&amp;M</t>
         </is>
       </c>
       <c r="D2" s="23" t="inlineStr">
         <is>
-          <t>Frais de livraison</t>
+          <t>Frais de maintien divers</t>
         </is>
       </c>
       <c r="E2" s="23" t="inlineStr">
         <is>
-          <t>204557218-108434242</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="F2" s="23" t="inlineStr">
         <is>
-          <t>Envoi DHL Express (bordereau 3157487874) - Miss Pretty Lashes</t>
+          <t>Vêtements (ceinture, robes, autre)</t>
         </is>
       </c>
       <c r="G2" s="24" t="n">
-        <v>35.06</v>
+        <v>148.1</v>
       </c>
       <c r="H2" s="24" t="n">
-        <v>1.75</v>
+        <v>7.41</v>
       </c>
       <c r="I2" s="24" t="n">
-        <v>3.5</v>
+        <v>14.77</v>
       </c>
       <c r="J2" s="24" t="n">
-        <v>40.31</v>
+        <v>170.28</v>
       </c>
       <c r="K2" s="23" t="inlineStr">
         <is>
-          <t>photo (lue par IA), taxes calculées</t>
+          <t>PDF (lu par IA)</t>
         </is>
       </c>
       <c r="L2" s="25" t="inlineStr">
         <is>
-          <t>Confirmation de paiement en français et en anglais (même transaction, comptée une seule fois). Aucun montant de taxe imprimé. Annotations manuscrites TVQ/TPS ignorées (sans « ? »). Numéro de facture = ID de transaction. ; TPS/TVQ calculées à partir du total taxes incluses (40.31 $ = 35.06 HT + 1.75 TPS 5 % + 3.50 TVQ 9,975 %) ; Date 2026-06-24 hors du trimestre 2026-T3</t>
+          <t>Date 2026-06-07 hors du trimestre 2026-T3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="23" t="inlineStr">
         <is>
-          <t>2026-T3/IMG_2959.jpeg</t>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
         </is>
       </c>
       <c r="B3" s="23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="C3" s="23" t="inlineStr">
         <is>
-          <t>La perle virtuelle</t>
+          <t>Scores P.A.T.</t>
         </is>
       </c>
       <c r="D3" s="23" t="inlineStr">
         <is>
-          <t>Soutien technique</t>
+          <t>Frais de maintien divers</t>
         </is>
       </c>
       <c r="E3" s="23" t="inlineStr">
         <is>
-          <t>26005</t>
+          <t>1883568-1</t>
         </is>
       </c>
       <c r="F3" s="23" t="inlineStr">
         <is>
-          <t>Journée de contenu - Présentiel (soutien technique et administratif, création de contenu, gestion de projet)</t>
+          <t>Repas restaurant</t>
         </is>
       </c>
       <c r="G3" s="24" t="n">
-        <v>595</v>
+        <v>42.35</v>
       </c>
       <c r="H3" s="24" t="n">
-        <v>29.75</v>
+        <v>2.12</v>
       </c>
       <c r="I3" s="24" t="n">
-        <v>59.35</v>
+        <v>4.22</v>
       </c>
       <c r="J3" s="24" t="n">
-        <v>684.1</v>
+        <v>48.69</v>
       </c>
       <c r="K3" s="23" t="inlineStr">
         <is>
-          <t>photo (lue par IA)</t>
-        </is>
-      </c>
-      <c r="L3" s="23" t="inlineStr"/>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L3" s="25" t="inlineStr">
+        <is>
+          <t>Date 2026-06-14 hors du trimestre 2026-T3</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="23" t="inlineStr">
         <is>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>Dollar Max Depot (Lachenaie)</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>Frais de maintien divers</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>850823</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>Paille de papier et ruban déco</t>
+        </is>
+      </c>
+      <c r="G4" s="24" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="H4" s="24" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I4" s="24" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J4" s="24" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="K4" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L4" s="25" t="inlineStr">
+        <is>
+          <t>Numéro de transaction utilisé comme numéro de facture ; Date 2026-06-14 hors du trimestre 2026-T3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>Michaels</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>Frais de maintien divers</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>4183932</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>Fournitures créatives (frisures, ficelle, rubans, ballon)</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="n">
+        <v>49.94</v>
+      </c>
+      <c r="H5" s="24" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I5" s="24" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="J5" s="24" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="K5" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L5" s="25" t="inlineStr">
+        <is>
+          <t>Reçu partiellement flou ; Date 2026-06-21 hors du trimestre 2026-T3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>VL Top Lash</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>Pinces SKYE (x2)</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="H6" s="24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="24" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="J6" s="24" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K6" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA), taxe combinée répartie</t>
+        </is>
+      </c>
+      <c r="L6" s="25" t="inlineStr">
+        <is>
+          <t>Montants du total final après réduction de 10,00 $ (taxe 4,49 $). ; TPS/TVQ réparties à partir de la taxe combinée imprimée (4.49 $ = 1.50 TPS 5 % + 2.99 TVQ 9,975 %) ; Date 2026-06-24 hors du trimestre 2026-T3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/IMG_2964.jpeg</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>DHL Express</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>Frais de livraison</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>204557218-108434242</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>Envoi DHL Express (bordereau 3157487874, expéditeur MISS PRETTY LASHES)</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="n">
+        <v>35.06</v>
+      </c>
+      <c r="H7" s="24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I7" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J7" s="24" t="n">
+        <v>40.31</v>
+      </c>
+      <c r="K7" s="23" t="inlineStr">
+        <is>
+          <t>photo (lue par IA), taxes calculées</t>
+        </is>
+      </c>
+      <c r="L7" s="25" t="inlineStr">
+        <is>
+          <t>Confirmation de paiement en français et en anglais (même transaction, comptée une seule fois). Aucun montant de taxe imprimé. Annotations manuscrites TPS/TVQ avec flèches ignorées. Numéro de facture = ID de transaction. ; TPS/TVQ calculées à partir du total taxes incluses (40.31 $ = 35.06 HT + 1.75 TPS 5 % + 3.50 TVQ 9,975 %) ; Date 2026-06-24 hors du trimestre 2026-T3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>Lashtoniic (commande Lbl extensions)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>1708</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>Sérum pour cils Lashtoniic, 12 unités + présentoir</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="n">
+        <v>239.88</v>
+      </c>
+      <c r="H8" s="24" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="I8" s="24" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="J8" s="24" t="n">
+        <v>275.8</v>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L8" s="25" t="inlineStr">
+        <is>
+          <t>Nom du fournisseur déduit du produit; livraison gratuite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr"/>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>Frais de service en ligne Shopify</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="n">
+        <v>24.51</v>
+      </c>
+      <c r="H9" s="24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="I9" s="24" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J9" s="24" t="n">
+        <v>28.18</v>
+      </c>
+      <c r="K9" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA), taxes calculées</t>
+        </is>
+      </c>
+      <c r="L9" s="25" t="inlineStr">
+        <is>
+          <t>Transaction en attente sur carte; aucune taxe détaillée. ; TPS/TVQ calculées à partir du total taxes incluses (28.18 $ = 24.51 HT + 1.23 TPS 5 % + 2.44 TVQ 9,975 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>Amazon.ca (LLBA Professional)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr"/>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>Écrans de rehaussement de cils Curacoro</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="n">
+        <v>18.93</v>
+      </c>
+      <c r="H10" s="24" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I10" s="24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J10" s="24" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA), taxes calculées</t>
+        </is>
+      </c>
+      <c r="L10" s="25" t="inlineStr">
+        <is>
+          <t>Taxes incluses non détaillées; total après code promo 2,20 $. Date déduite (livraison 'demain 9 juill.'), note manuscrite peu lisible. ; TPS/TVQ calculées à partir du total taxes incluses (21.76 $ = 18.93 HT + 0.95 TPS 5 % + 1.88 TVQ 9,975 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/IMG_2959.jpeg</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>La perle virtuelle</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>Soutien technique</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>26005</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>Journée de contenu - Présentiel (soutien technique et administratif, création de contenu, gestion de projet)</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="n">
+        <v>595</v>
+      </c>
+      <c r="H11" s="24" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="I11" s="24" t="n">
+        <v>59.35</v>
+      </c>
+      <c r="J11" s="24" t="n">
+        <v>684.1</v>
+      </c>
+      <c r="K11" s="23" t="inlineStr">
+        <is>
+          <t>photo (lue par IA)</t>
+        </is>
+      </c>
+      <c r="L11" s="23" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>Amazon.ca (StarsColors)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr"/>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>Trousse de rehaussement de cils ICONSIGN</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="H12" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I12" s="24" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J12" s="24" t="n">
+        <v>19.53</v>
+      </c>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA), taxes calculées</t>
+        </is>
+      </c>
+      <c r="L12" s="25" t="inlineStr">
+        <is>
+          <t>Taxes incluses non détaillées. Date selon note manuscrite/livraison. ; TPS/TVQ calculées à partir du total taxes incluses (19.53 $ = 16.99 HT + 0.85 TPS 5 % + 1.69 TVQ 9,975 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>Patrick Morin</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>04F021303246</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>Extincteur d'incendie</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="n">
+        <v>27.99</v>
+      </c>
+      <c r="H13" s="24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I13" s="24" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="J13" s="24" t="n">
+        <v>32.18</v>
+      </c>
+      <c r="K13" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L13" s="23" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>Dollarama</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>Frais de maintien divers</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>3348</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>Articles divers (Anjou)</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="n">
+        <v>30.36</v>
+      </c>
+      <c r="H14" s="24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I14" s="24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J14" s="24" t="n">
+        <v>34.19</v>
+      </c>
+      <c r="K14" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L14" s="25" t="inlineStr">
+        <is>
+          <t>Sous-total inclut des dépôts de consigne</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>DHL Express</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>Frais de livraison</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>5477755522</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>Frais de livraison DHL (envoi de Miss Pretty Lashes)</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I15" s="24" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J15" s="24" t="n">
+        <v>30.38</v>
+      </c>
+      <c r="K15" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA), taxes calculées</t>
+        </is>
+      </c>
+      <c r="L15" s="25" t="inlineStr">
+        <is>
+          <t>Numéro de bordereau utilisé comme numéro de facture. Aucune taxe détaillée. ; TPS/TVQ calculées à partir du total taxes incluses (30.38 $ = 26.42 HT + 1.32 TPS 5 % + 2.64 TVQ 9,975 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>Amazon.ca</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr"/>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>Tabouret hydraulique Master Massage</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="n">
+        <v>109.98</v>
+      </c>
+      <c r="H16" s="24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I16" s="24" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="J16" s="24" t="n">
+        <v>126.45</v>
+      </c>
+      <c r="K16" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA), taxes calculées</t>
+        </is>
+      </c>
+      <c r="L16" s="25" t="inlineStr">
+        <is>
+          <t>Taxes incluses non détaillées. Date déduite (livraison 'demain 16 juill.'; note manuscrite peu lisible). ; TPS/TVQ calculées à partir du total taxes incluses (126.45 $ = 109.98 HT + 5.50 TPS 5 % + 10.97 TVQ 9,975 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>Amazon.ca (LLBA Professional)</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr"/>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>Extensions de cils Curacoro</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="H17" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I17" s="24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J17" s="24" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="K17" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA), taxes calculées</t>
+        </is>
+      </c>
+      <c r="L17" s="25" t="inlineStr">
+        <is>
+          <t>Taxes incluses non détaillées. Date selon note manuscrite. ; TPS/TVQ calculées à partir du total taxes incluses (18.46 $ = 16.06 HT + 0.80 TPS 5 % + 1.60 TVQ 9,975 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>Amazon.ca</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>702-3892259-3321860</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>Mouchoirs faciaux en velours Royale</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="H18" s="24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I18" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="24" t="n">
+        <v>36.74</v>
+      </c>
+      <c r="K18" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L18" s="25" t="inlineStr">
+        <is>
+          <t>TVQ imprimée à 0,00 $ sur le document; TPS 1,75 $.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>Amazon.com.ca ULC</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>CA82J18PMACCUI</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>Royale Velour mouchoirs faciaux 24 boîtes</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="H19" s="24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I19" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="24" t="n">
+        <v>36.74</v>
+      </c>
+      <c r="K19" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L19" s="25" t="inlineStr">
+        <is>
+          <t>TVQ imprimée à 0,00 $</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>Amazon.com.ca (qingdaoweimeishijiexinxikejiyouxiangongsi)</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>CA899UIFFIII</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>VEYES INC extensions de cils volume classique</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="H20" s="24" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I20" s="24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J20" s="24" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="K20" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L20" s="23" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>Amazon.ca</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr"/>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>Articles (2) – matériel de cils</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="n">
+        <v>27.53</v>
+      </c>
+      <c r="H21" s="24" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I21" s="24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J21" s="24" t="n">
+        <v>30.87</v>
+      </c>
+      <c r="K21" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L21" s="25" t="inlineStr">
+        <is>
+          <t>HT = 32,78 $ − coupons 2,10 $ − promotion 3,15 $. Date selon note manuscrite/livraison.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>La Perle Virtuelle</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>Soutien technique</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>26009</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>Gestion opérationnelle – soutien technique et administratif</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H22" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="I22" s="24" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="J22" s="24" t="n">
+        <v>1149.75</v>
+      </c>
+      <c r="K22" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L22" s="23" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>Amazon.ca</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>702-1576304-8553019</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>Poudre coréenne de cils PERMANIA + coussinets (lot)</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="n">
+        <v>45.97</v>
+      </c>
+      <c r="H23" s="24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I23" s="24" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="J23" s="24" t="n">
+        <v>52.85</v>
+      </c>
+      <c r="K23" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L23" s="25" t="inlineStr">
+        <is>
+          <t>Même commande que la facture CA6G3SHGH4HI (page suivante) : risque de double comptage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>Amazon.ca (vendeur : putianshiqianmuhemaoyiyouxiangongsi)</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>CA6G3SHGH4HI</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>Lash Lift Pads Kit, 3 paires (utuher)</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="H24" s="24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I24" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="24" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="K24" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L24" s="25" t="inlineStr">
+        <is>
+          <t>Facture partielle de la commande 702-1576304-8553019 (déjà incluse dans le total 52,85 $) : possible doublon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr"/>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>Livraison Uber (Courier Saver)</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="n">
+        <v>14.39</v>
+      </c>
+      <c r="H25" s="24" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="I25" s="24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="J25" s="24" t="n">
+        <v>16.54</v>
+      </c>
+      <c r="K25" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA), taxes calculées</t>
+        </is>
+      </c>
+      <c r="L25" s="25" t="inlineStr">
+        <is>
+          <t>Aucune taxe détaillée. ; TPS/TVQ calculées à partir du total taxes incluses (16.54 $ = 14.39 HT + 0.72 TPS 5 % + 1.43 TVQ 9,975 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>Amazon.ca (EXYGLO)</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>702-0686830-7305820</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>Lot de 10 boîtes d'expédition (récapitulatif de commande)</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="n">
+        <v>58.98</v>
+      </c>
+      <c r="H26" s="24" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="I26" s="24" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="J26" s="24" t="n">
+        <v>67.81999999999999</v>
+      </c>
+      <c r="K26" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L26" s="25" t="inlineStr">
+        <is>
+          <t>Capture d'écran du récapitulatif de commande, numéro de commande utilisé comme numéro de facture</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>Amazon.ca</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr"/>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>Articles (2) – matériel de cils (dont boîtes d'expédition EXYGLO)</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="n">
+        <v>58.98</v>
+      </c>
+      <c r="H27" s="24" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="I27" s="24" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="J27" s="24" t="n">
+        <v>67.81999999999999</v>
+      </c>
+      <c r="K27" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L27" s="25" t="inlineStr">
+        <is>
+          <t>Date selon note manuscrite (livraison prévue 20 août).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
           <t>2026-T3/IMG_2962.jpeg</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>Canadian Tire #928</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>Matériel de cils</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>TRANS 139</t>
         </is>
       </c>
-      <c r="F4" s="23" t="inlineStr">
-        <is>
-          <t>GLD BLEU P50 45 (article de quincaillerie)</t>
-        </is>
-      </c>
-      <c r="G4" s="24" t="n">
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>GLD BLEU P50 45 (article Canadian Tire)</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="n">
         <v>13.99</v>
       </c>
-      <c r="H4" s="24" t="n">
+      <c r="H28" s="24" t="n">
         <v>0.7</v>
       </c>
-      <c r="I4" s="24" t="n">
+      <c r="I28" s="24" t="n">
         <v>1.4</v>
       </c>
-      <c r="J4" s="24" t="n">
+      <c r="J28" s="24" t="n">
         <v>16.09</v>
       </c>
-      <c r="K4" s="23" t="inlineStr">
+      <c r="K28" s="23" t="inlineStr">
         <is>
           <t>photo (lue par IA)</t>
         </is>
       </c>
-      <c r="L4" s="25" t="inlineStr">
-        <is>
-          <t>Date imprimée 08/25/2026; annotation manuscrite « oct 2026 » ignorée. TVQ imprimée 1,40 (9,975 % de 13,99 = 1,395).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="L28" s="25" t="inlineStr">
+        <is>
+          <t>Annotation manuscrite « oct 2026 » ignorée. Date imprimée 08/25/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>Amazon.com.ca ULC</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>CA62ZJ7TIACCUI</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>Ring Pop Candy 50 unités</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="H29" s="24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I29" s="24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J29" s="24" t="n">
+        <v>35.81</v>
+      </c>
+      <c r="K29" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L29" s="23" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>Dollarama</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>Frais de maintien divers</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>4318</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>Articles divers (Sherbrooke Est)</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H30" s="24" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I30" s="24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J30" s="24" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L30" s="25" t="inlineStr">
+        <is>
+          <t>Numéro de facture partiellement illisible</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>Maxi &amp; Cie (Montréal Versailles)</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>Frais de maintien divers</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr"/>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="H31" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="24" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="J31" s="24" t="n">
+        <v>45.97</v>
+      </c>
+      <c r="K31" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L31" s="25" t="inlineStr">
+        <is>
+          <t>Reçu à l'envers; date 26/09/10; référence 142336</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>La Perle Virtuelle</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>Soutien technique</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>26013</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>Gestion opérationnelle - présence mensuelle</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="n">
+        <v>500</v>
+      </c>
+      <c r="H32" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="I32" s="24" t="n">
+        <v>49.87</v>
+      </c>
+      <c r="J32" s="24" t="n">
+        <v>574.88</v>
+      </c>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L32" s="23" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>DHL Express Canada Ltd</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>Frais de livraison</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
+        <is>
+          <t>E103255297400</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>Droits et frais de dédouanement</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="n">
+        <v>30.93</v>
+      </c>
+      <c r="H33" s="24" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="I33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="24" t="n">
+        <v>38.09</v>
+      </c>
+      <c r="K33" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L33" s="25" t="inlineStr">
+        <is>
+          <t>TPS sur importation 4,82 $ + TPS sur frais de dédouanement 2,34 $</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>Amazon.com.ca (guangzhouxingyanshengwukejiyouxiangongsi)</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="inlineStr">
+        <is>
+          <t>CA63XQ7BDOQI</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>Trousse de rehaussement de cils ICONSIGN</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="H34" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I34" s="24" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J34" s="24" t="n">
+        <v>19.53</v>
+      </c>
+      <c r="K34" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L34" s="23" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>Amazon.com.ca (guangzhouxingyanshengwukejiyouxiangongsi)</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
+        <is>
+          <t>CA63XG7BDOOI</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>Fast Perm Lash Lift Kit</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="H35" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I35" s="24" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J35" s="24" t="n">
+        <v>19.53</v>
+      </c>
+      <c r="K35" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L35" s="25" t="inlineStr">
+        <is>
+          <t>Même montant que la facture précédente mais numéro de facture et commande différents</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
+        </is>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>Amazon.com.ca (Shanghai Xijian Technology Co., Ltd)</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E36" s="23" t="inlineStr">
+        <is>
+          <t>CA6GGKGO4C6I</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>Article ASIN B08BQXSRR7</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="H36" s="24" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I36" s="24" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J36" s="24" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="K36" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L36" s="25" t="inlineStr">
+        <is>
+          <t>Prix 10,99 $ moins rabais 1,10 $</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
+        </is>
+      </c>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C37" s="23" t="inlineStr">
+        <is>
+          <t>DHL Express Canada Ltd</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="inlineStr">
+        <is>
+          <t>Frais de livraison</t>
+        </is>
+      </c>
+      <c r="E37" s="23" t="inlineStr">
+        <is>
+          <t>E103278805700</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>Droits et frais de dédouanement</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="n">
+        <v>76.06</v>
+      </c>
+      <c r="H37" s="24" t="n">
+        <v>23.97</v>
+      </c>
+      <c r="I37" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="24" t="n">
+        <v>100.03</v>
+      </c>
+      <c r="K37" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L37" s="25" t="inlineStr">
+        <is>
+          <t>TPS sur importation 21,63 $ + TPS sur frais de dédouanement 2,34 $</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
+        </is>
+      </c>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C38" s="23" t="inlineStr">
+        <is>
+          <t>Dollarama</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="inlineStr">
+        <is>
+          <t>Frais de maintien divers</t>
+        </is>
+      </c>
+      <c r="E38" s="23" t="inlineStr">
+        <is>
+          <t>7942</t>
+        </is>
+      </c>
+      <c r="F38" s="23" t="inlineStr">
+        <is>
+          <t>Effaces magiques et cadres document</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H38" s="24" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I38" s="24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J38" s="24" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="K38" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L38" s="25" t="inlineStr">
+        <is>
+          <t>Date 2026-10-04 hors du trimestre 2026-T3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+        </is>
+      </c>
+      <c r="B39" s="23" t="n"/>
+      <c r="C39" s="23" t="inlineStr">
+        <is>
+          <t>Fournisseur non indiqué (commande en ligne, livraison à Montréal)</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="inlineStr"/>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>Marchandise et expédition</t>
+        </is>
+      </c>
+      <c r="G39" s="24" t="n">
+        <v>517.28</v>
+      </c>
+      <c r="H39" s="24" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="I39" s="24" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="J39" s="24" t="n">
+        <v>594.74</v>
+      </c>
+      <c r="K39" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA), taxe combinée répartie</t>
+        </is>
+      </c>
+      <c r="L39" s="25" t="inlineStr">
+        <is>
+          <t>Fournisseur et date non visibles. Sous-total 507,29 $ + expédition 9,99 $. Taxes de vente combinées 77,46 $. ; TPS/TVQ réparties à partir de la taxe combinée imprimée (77.46 $ = 25.86 TPS 5 % + 51.60 TVQ 9,975 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+        </is>
+      </c>
+      <c r="B40" s="23" t="n"/>
+      <c r="C40" s="23" t="inlineStr">
+        <is>
+          <t>NovoQueen Pro</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
+        <is>
+          <t>MF04A537Y</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>L'expérience Glow &amp; Grow 2027 (formation)</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="n">
+        <v>555</v>
+      </c>
+      <c r="H40" s="24" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="I40" s="24" t="n">
+        <v>55.36</v>
+      </c>
+      <c r="J40" s="24" t="n">
+        <v>638.11</v>
+      </c>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA), taxe combinée répartie</t>
+        </is>
+      </c>
+      <c r="L40" s="25" t="inlineStr">
+        <is>
+          <t>Taxes estimées combinées 83,11 $. Date non visible. ; TPS/TVQ réparties à partir de la taxe combinée imprimée (83.11 $ = 27.75 TPS 5 % + 55.36 TVQ 9,975 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+        </is>
+      </c>
+      <c r="B41" s="23" t="n"/>
+      <c r="C41" s="23" t="inlineStr">
+        <is>
+          <t>Temu (présumé, application d'achat en ligne)</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="inlineStr"/>
+      <c r="F41" s="23" t="inlineStr">
+        <is>
+          <t>Commande de 20 articles (brosses à cils, etc.)</t>
+        </is>
+      </c>
+      <c r="G41" s="24" t="n">
+        <v>249.4</v>
+      </c>
+      <c r="H41" s="24" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="I41" s="24" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="J41" s="24" t="n">
+        <v>286.74</v>
+      </c>
+      <c r="K41" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L41" s="25" t="inlineStr">
+        <is>
+          <t>Taxes incluses détaillées (GST 12,46 $ / QST 24,88 $; total 37,34 $). HT calculé = total − taxes. Fournisseur et date non visibles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+        </is>
+      </c>
+      <c r="B42" s="23" t="n"/>
+      <c r="C42" s="23" t="inlineStr">
+        <is>
+          <t>ZAHKA SNC</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>Service d'accompagnement en ligne de marque</t>
+        </is>
+      </c>
+      <c r="E42" s="23" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="F42" s="23" t="inlineStr">
+        <is>
+          <t>Service d'accompagnement en image de marque</t>
+        </is>
+      </c>
+      <c r="G42" s="24" t="n">
+        <v>400</v>
+      </c>
+      <c r="H42" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="I42" s="24" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="J42" s="24" t="n">
+        <v>459.9</v>
+      </c>
+      <c r="K42" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L42" s="25" t="inlineStr">
+        <is>
+          <t>Date non imprimée (août 2026 selon note manuscrite).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+        </is>
+      </c>
+      <c r="B43" s="23" t="n"/>
+      <c r="C43" s="23" t="inlineStr">
+        <is>
+          <t>Muhammad Adnan Muhammad Aslam (virement)</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E43" s="23" t="inlineStr"/>
+      <c r="F43" s="23" t="inlineStr">
+        <is>
+          <t>Pinces à cils (virement)</t>
+        </is>
+      </c>
+      <c r="G43" s="24" t="n">
+        <v>375.76</v>
+      </c>
+      <c r="H43" s="24" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="I43" s="24" t="n">
+        <v>37.48</v>
+      </c>
+      <c r="J43" s="24" t="n">
+        <v>432.03</v>
+      </c>
+      <c r="K43" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA), taxes calculées</t>
+        </is>
+      </c>
+      <c r="L43" s="25" t="inlineStr">
+        <is>
+          <t>Confirmation de virement seulement, aucune taxe imprimée; date non visible (août 2026 selon note manuscrite). ; TPS/TVQ calculées à partir du total taxes incluses (432.03 $ = 375.76 HT + 18.79 TPS 5 % + 37.48 TVQ 9,975 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="26" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" s="26" t="n"/>
-      <c r="C5" s="26" t="n"/>
-      <c r="D5" s="26" t="n"/>
-      <c r="E5" s="26" t="n"/>
-      <c r="F5" s="26" t="n"/>
-      <c r="G5" s="27" t="n">
-        <v>644.05</v>
-      </c>
-      <c r="H5" s="27" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="I5" s="27" t="n">
-        <v>64.25</v>
-      </c>
-      <c r="J5" s="26" t="n"/>
-      <c r="K5" s="26" t="n"/>
-      <c r="L5" s="26" t="n"/>
+      <c r="B44" s="26" t="n"/>
+      <c r="C44" s="26" t="n"/>
+      <c r="D44" s="26" t="n"/>
+      <c r="E44" s="26" t="n"/>
+      <c r="F44" s="26" t="n"/>
+      <c r="G44" s="27" t="n">
+        <v>5577.05</v>
+      </c>
+      <c r="H44" s="27" t="n">
+        <v>303.61</v>
+      </c>
+      <c r="I44" s="27" t="n">
+        <v>538.1799999999999</v>
+      </c>
+      <c r="J44" s="26" t="n"/>
+      <c r="K44" s="26" t="n"/>
+      <c r="L44" s="26" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/orders/2026-T3_declaration_tps_tvq.xlsx
+++ b/data/orders/2026-T3_declaration_tps_tvq.xlsx
@@ -802,17 +802,17 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Dépenses (42 pièces)</t>
+          <t>Dépenses (44 pièces)</t>
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>5577.05</v>
+        <v>7863.35</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>303.61</v>
+        <v>417.94</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>538.1799999999999</v>
+        <v>766.25</v>
       </c>
     </row>
     <row r="20">
@@ -875,10 +875,10 @@
       </c>
       <c r="D25" s="14" t="n"/>
       <c r="E25" s="13" t="n">
-        <v>-303.61</v>
+        <v>-417.94</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>-538.1799999999999</v>
+        <v>-766.25</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -890,16 +890,16 @@
       </c>
       <c r="D26" s="16" t="n"/>
       <c r="E26" s="18" t="n">
-        <v>182.06</v>
+        <v>67.73</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>426.46</v>
+        <v>198.39</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>TPS : 182,06 $ à payer à Revenu Québec</t>
+          <t>TPS : 67,73 $ à payer à Revenu Québec</t>
         </is>
       </c>
       <c r="C28" s="20" t="n"/>
@@ -910,7 +910,7 @@
     <row r="29" ht="24" customHeight="1">
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>TVQ : 426,46 $ à payer à Revenu Québec</t>
+          <t>TVQ : 198,39 $ à payer à Revenu Québec</t>
         </is>
       </c>
       <c r="C29" s="20" t="n"/>
@@ -948,7 +948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="L2" s="25" t="inlineStr">
         <is>
-          <t>Date 2026-06-07 hors du trimestre 2026-T3</t>
+          <t>Date 2026-06-07 hors du trimestre 2026-T3 ; Date 2026-06-07 hors du trimestre 2026-T3</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="L3" s="25" t="inlineStr">
         <is>
-          <t>Date 2026-06-14 hors du trimestre 2026-T3</t>
+          <t>Date 2026-06-14 hors du trimestre 2026-T3 ; Date 2026-06-14 hors du trimestre 2026-T3</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="L4" s="25" t="inlineStr">
         <is>
-          <t>Numéro de transaction utilisé comme numéro de facture ; Date 2026-06-14 hors du trimestre 2026-T3</t>
+          <t>Numéro de transaction utilisé comme numéro de facture ; Date 2026-06-14 hors du trimestre 2026-T3 ; Date 2026-06-14 hors du trimestre 2026-T3</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="L5" s="25" t="inlineStr">
         <is>
-          <t>Reçu partiellement flou ; Date 2026-06-21 hors du trimestre 2026-T3</t>
+          <t>Reçu partiellement flou ; Date 2026-06-21 hors du trimestre 2026-T3 ; Date 2026-06-21 hors du trimestre 2026-T3</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L6" s="25" t="inlineStr">
         <is>
-          <t>Montants du total final après réduction de 10,00 $ (taxe 4,49 $). ; TPS/TVQ réparties à partir de la taxe combinée imprimée (4.49 $ = 1.50 TPS 5 % + 2.99 TVQ 9,975 %) ; Date 2026-06-24 hors du trimestre 2026-T3</t>
+          <t>Montants du total final après réduction de 10,00 $ (taxe 4,49 $). ; TPS/TVQ réparties à partir de la taxe combinée imprimée (4.49 $ = 1.50 TPS 5 % + 2.99 TVQ 9,975 %) ; Date 2026-06-24 hors du trimestre 2026-T3 ; Date 2026-06-24 hors du trimestre 2026-T3</t>
         </is>
       </c>
     </row>
@@ -1347,24 +1347,24 @@
       </c>
       <c r="L7" s="25" t="inlineStr">
         <is>
-          <t>Confirmation de paiement en français et en anglais (même transaction, comptée une seule fois). Aucun montant de taxe imprimé. Annotations manuscrites TPS/TVQ avec flèches ignorées. Numéro de facture = ID de transaction. ; TPS/TVQ calculées à partir du total taxes incluses (40.31 $ = 35.06 HT + 1.75 TPS 5 % + 3.50 TVQ 9,975 %) ; Date 2026-06-24 hors du trimestre 2026-T3</t>
+          <t>Confirmation de paiement en français et en anglais (même transaction, comptée une seule fois). Aucun montant de taxe imprimé. Annotations manuscrites TPS/TVQ avec flèches ignorées. Numéro de facture = ID de transaction. ; TPS/TVQ calculées à partir du total taxes incluses (40.31 $ = 35.06 HT + 1.75 TPS 5 % + 3.50 TVQ 9,975 %) ; Date 2026-06-24 hors du trimestre 2026-T3 ; Date 2026-06-24 hors du trimestre 2026-T3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
         <is>
-          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+          <t>2026-T3/Telus_PRET.jpeg</t>
         </is>
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>Lashtoniic (commande Lbl extensions)</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -1372,36 +1372,32 @@
           <t>Matériel de cils</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
-        <is>
-          <t>1708</t>
-        </is>
-      </c>
+      <c r="E8" s="23" t="inlineStr"/>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>Sérum pour cils Lashtoniic, 12 unités + présentoir</t>
+          <t>iPhone 17 Pro Max 256 Go Argent (prêt Affirm, 24 mois)</t>
         </is>
       </c>
       <c r="G8" s="24" t="n">
-        <v>239.88</v>
+        <v>1749</v>
       </c>
       <c r="H8" s="24" t="n">
-        <v>11.99</v>
+        <v>87.45</v>
       </c>
       <c r="I8" s="24" t="n">
-        <v>23.93</v>
+        <v>174.46</v>
       </c>
       <c r="J8" s="24" t="n">
-        <v>275.8</v>
+        <v>2010.91</v>
       </c>
       <c r="K8" s="23" t="inlineStr">
         <is>
-          <t>PDF (lu par IA)</t>
+          <t>photo (lue par IA), taxe combinée répartie</t>
         </is>
       </c>
       <c r="L8" s="25" t="inlineStr">
         <is>
-          <t>Nom du fournisseur déduit du produit; livraison gratuite.</t>
+          <t>Impôts/taxes de 261,91 $ imprimés sans distinction TPS/TVQ (à calculer, repère « ? » de l'entreprise). Prêt de 1 749,00 $ (72,88 $/mois x 24). Total = prêt + taxes (calculé). Date non imprimée : période juillet 2026 selon la note manuscrite. ; TPS/TVQ réparties à partir de la taxe combinée imprimée (261.91 $ = 87.45 TPS 5 % + 174.46 TVQ 9,975 %)</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1409,12 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>Shopify Inc.</t>
+          <t>Lashtoniic (commande Lbl extensions)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -1426,32 +1422,36 @@
           <t>Matériel de cils</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr"/>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>1708</t>
+        </is>
+      </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t>Frais de service en ligne Shopify</t>
+          <t>Sérum pour cils Lashtoniic, 12 unités + présentoir</t>
         </is>
       </c>
       <c r="G9" s="24" t="n">
-        <v>24.51</v>
+        <v>239.88</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>1.23</v>
+        <v>11.99</v>
       </c>
       <c r="I9" s="24" t="n">
-        <v>2.44</v>
+        <v>23.93</v>
       </c>
       <c r="J9" s="24" t="n">
-        <v>28.18</v>
+        <v>275.8</v>
       </c>
       <c r="K9" s="23" t="inlineStr">
         <is>
-          <t>PDF (lu par IA), taxes calculées</t>
+          <t>PDF (lu par IA)</t>
         </is>
       </c>
       <c r="L9" s="25" t="inlineStr">
         <is>
-          <t>Transaction en attente sur carte; aucune taxe détaillée. ; TPS/TVQ calculées à partir du total taxes incluses (28.18 $ = 24.51 HT + 1.23 TPS 5 % + 2.44 TVQ 9,975 %)</t>
+          <t>Nom du fournisseur déduit du produit; livraison gratuite.</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>Amazon.ca (LLBA Professional)</t>
+          <t>Shopify Inc.</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -1479,20 +1479,20 @@
       <c r="E10" s="23" t="inlineStr"/>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t>Écrans de rehaussement de cils Curacoro</t>
+          <t>Frais de service en ligne Shopify</t>
         </is>
       </c>
       <c r="G10" s="24" t="n">
-        <v>18.93</v>
+        <v>24.51</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>0.95</v>
+        <v>1.23</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>1.88</v>
+        <v>2.44</v>
       </c>
       <c r="J10" s="24" t="n">
-        <v>21.76</v>
+        <v>28.18</v>
       </c>
       <c r="K10" s="23" t="inlineStr">
         <is>
@@ -1501,14 +1501,14 @@
       </c>
       <c r="L10" s="25" t="inlineStr">
         <is>
-          <t>Taxes incluses non détaillées; total après code promo 2,20 $. Date déduite (livraison 'demain 9 juill.'), note manuscrite peu lisible. ; TPS/TVQ calculées à partir du total taxes incluses (21.76 $ = 18.93 HT + 0.95 TPS 5 % + 1.88 TVQ 9,975 %)</t>
+          <t>Transaction en attente sur carte; aucune taxe détaillée. ; TPS/TVQ calculées à partir du total taxes incluses (28.18 $ = 24.51 HT + 1.23 TPS 5 % + 2.44 TVQ 9,975 %)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>2026-T3/IMG_2959.jpeg</t>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
         </is>
       </c>
       <c r="B11" s="23" t="inlineStr">
@@ -1518,107 +1518,107 @@
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>La perle virtuelle</t>
+          <t>Amazon.ca (LLBA Professional)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
-          <t>Soutien technique</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="inlineStr">
-        <is>
-          <t>26005</t>
-        </is>
-      </c>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr"/>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>Journée de contenu - Présentiel (soutien technique et administratif, création de contenu, gestion de projet)</t>
+          <t>Écrans de rehaussement de cils Curacoro</t>
         </is>
       </c>
       <c r="G11" s="24" t="n">
-        <v>595</v>
+        <v>18.93</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>29.75</v>
+        <v>0.95</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>59.35</v>
+        <v>1.88</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>684.1</v>
+        <v>21.76</v>
       </c>
       <c r="K11" s="23" t="inlineStr">
         <is>
-          <t>photo (lue par IA)</t>
-        </is>
-      </c>
-      <c r="L11" s="23" t="inlineStr"/>
+          <t>PDF (lu par IA), taxes calculées</t>
+        </is>
+      </c>
+      <c r="L11" s="25" t="inlineStr">
+        <is>
+          <t>Taxes incluses non détaillées; total après code promo 2,20 $. Date déduite (livraison 'demain 9 juill.'), note manuscrite peu lisible. ; TPS/TVQ calculées à partir du total taxes incluses (21.76 $ = 18.93 HT + 0.95 TPS 5 % + 1.88 TVQ 9,975 %)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="23" t="inlineStr">
         <is>
-          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+          <t>2026-T3/IMG_2959.jpeg</t>
         </is>
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>Amazon.ca (StarsColors)</t>
+          <t>La perle virtuelle</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>Matériel de cils</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="inlineStr"/>
+          <t>Soutien technique</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>26005</t>
+        </is>
+      </c>
       <c r="F12" s="23" t="inlineStr">
         <is>
-          <t>Trousse de rehaussement de cils ICONSIGN</t>
+          <t>Journée de contenu - Présentiel (soutien technique et administratif, création de contenu, gestion de projet)</t>
         </is>
       </c>
       <c r="G12" s="24" t="n">
-        <v>16.99</v>
+        <v>595</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>0.85</v>
+        <v>29.75</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>1.69</v>
+        <v>59.35</v>
       </c>
       <c r="J12" s="24" t="n">
-        <v>19.53</v>
+        <v>684.1</v>
       </c>
       <c r="K12" s="23" t="inlineStr">
         <is>
-          <t>PDF (lu par IA), taxes calculées</t>
-        </is>
-      </c>
-      <c r="L12" s="25" t="inlineStr">
-        <is>
-          <t>Taxes incluses non détaillées. Date selon note manuscrite/livraison. ; TPS/TVQ calculées à partir du total taxes incluses (19.53 $ = 16.99 HT + 0.85 TPS 5 % + 1.69 TVQ 9,975 %)</t>
-        </is>
-      </c>
+          <t>photo (lue par IA)</t>
+        </is>
+      </c>
+      <c r="L12" s="23" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
         </is>
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>Patrick Morin</t>
+          <t>Amazon.ca (StarsColors)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -1626,34 +1626,34 @@
           <t>Matériel de cils</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>04F021303246</t>
-        </is>
-      </c>
+      <c r="E13" s="23" t="inlineStr"/>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>Extincteur d'incendie</t>
+          <t>Trousse de rehaussement de cils ICONSIGN</t>
         </is>
       </c>
       <c r="G13" s="24" t="n">
-        <v>27.99</v>
+        <v>16.99</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>1.4</v>
+        <v>0.85</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>2.79</v>
+        <v>1.69</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>32.18</v>
+        <v>19.53</v>
       </c>
       <c r="K13" s="23" t="inlineStr">
         <is>
-          <t>PDF (lu par IA)</t>
-        </is>
-      </c>
-      <c r="L13" s="23" t="inlineStr"/>
+          <t>PDF (lu par IA), taxes calculées</t>
+        </is>
+      </c>
+      <c r="L13" s="25" t="inlineStr">
+        <is>
+          <t>Taxes incluses non détaillées. Date selon note manuscrite/livraison. ; TPS/TVQ calculées à partir du total taxes incluses (19.53 $ = 16.99 HT + 0.85 TPS 5 % + 1.69 TVQ 9,975 %)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="23" t="inlineStr">
@@ -1663,103 +1663,99 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>Dollarama</t>
+          <t>Patrick Morin</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>Frais de maintien divers</t>
+          <t>Matériel de cils</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>04F021303246</t>
         </is>
       </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t>Articles divers (Anjou)</t>
+          <t>Extincteur d'incendie</t>
         </is>
       </c>
       <c r="G14" s="24" t="n">
-        <v>30.36</v>
+        <v>27.99</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>2.55</v>
+        <v>2.79</v>
       </c>
       <c r="J14" s="24" t="n">
-        <v>34.19</v>
+        <v>32.18</v>
       </c>
       <c r="K14" s="23" t="inlineStr">
         <is>
           <t>PDF (lu par IA)</t>
         </is>
       </c>
-      <c r="L14" s="25" t="inlineStr">
-        <is>
-          <t>Sous-total inclut des dépôts de consigne</t>
-        </is>
-      </c>
+      <c r="L14" s="23" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="23" t="inlineStr">
         <is>
-          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
         </is>
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>DHL Express</t>
+          <t>Dollarama</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>Frais de livraison</t>
+          <t>Frais de maintien divers</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
         <is>
-          <t>5477755522</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t>Frais de livraison DHL (envoi de Miss Pretty Lashes)</t>
+          <t>Articles divers (Anjou)</t>
         </is>
       </c>
       <c r="G15" s="24" t="n">
-        <v>26.42</v>
+        <v>30.36</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="J15" s="24" t="n">
-        <v>30.38</v>
+        <v>34.19</v>
       </c>
       <c r="K15" s="23" t="inlineStr">
         <is>
-          <t>PDF (lu par IA), taxes calculées</t>
+          <t>PDF (lu par IA)</t>
         </is>
       </c>
       <c r="L15" s="25" t="inlineStr">
         <is>
-          <t>Numéro de bordereau utilisé comme numéro de facture. Aucune taxe détaillée. ; TPS/TVQ calculées à partir du total taxes incluses (30.38 $ = 26.42 HT + 1.32 TPS 5 % + 2.64 TVQ 9,975 %)</t>
+          <t>Sous-total inclut des dépôts de consigne</t>
         </is>
       </c>
     </row>
@@ -1771,36 +1767,40 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>Amazon.ca</t>
+          <t>DHL Express</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>Matériel de cils</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr"/>
+          <t>Frais de livraison</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>5477755522</t>
+        </is>
+      </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>Tabouret hydraulique Master Massage</t>
+          <t>Frais de livraison DHL (envoi de Miss Pretty Lashes)</t>
         </is>
       </c>
       <c r="G16" s="24" t="n">
-        <v>109.98</v>
+        <v>26.42</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>5.5</v>
+        <v>1.32</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>10.97</v>
+        <v>2.64</v>
       </c>
       <c r="J16" s="24" t="n">
-        <v>126.45</v>
+        <v>30.38</v>
       </c>
       <c r="K16" s="23" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="L16" s="25" t="inlineStr">
         <is>
-          <t>Taxes incluses non détaillées. Date déduite (livraison 'demain 16 juill.'; note manuscrite peu lisible). ; TPS/TVQ calculées à partir du total taxes incluses (126.45 $ = 109.98 HT + 5.50 TPS 5 % + 10.97 TVQ 9,975 %)</t>
+          <t>Numéro de bordereau utilisé comme numéro de facture. Aucune taxe détaillée. ; TPS/TVQ calculées à partir du total taxes incluses (30.38 $ = 26.42 HT + 1.32 TPS 5 % + 2.64 TVQ 9,975 %)</t>
         </is>
       </c>
     </row>
@@ -1821,12 +1821,12 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>Amazon.ca (LLBA Professional)</t>
+          <t>Amazon.ca</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -1837,20 +1837,20 @@
       <c r="E17" s="23" t="inlineStr"/>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t>Extensions de cils Curacoro</t>
+          <t>Tabouret hydraulique Master Massage</t>
         </is>
       </c>
       <c r="G17" s="24" t="n">
-        <v>16.06</v>
+        <v>109.98</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>1.6</v>
+        <v>10.97</v>
       </c>
       <c r="J17" s="24" t="n">
-        <v>18.46</v>
+        <v>126.45</v>
       </c>
       <c r="K17" s="23" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="L17" s="25" t="inlineStr">
         <is>
-          <t>Taxes incluses non détaillées. Date selon note manuscrite. ; TPS/TVQ calculées à partir du total taxes incluses (18.46 $ = 16.06 HT + 0.80 TPS 5 % + 1.60 TVQ 9,975 %)</t>
+          <t>Taxes incluses non détaillées. Date déduite (livraison 'demain 16 juill.'; note manuscrite peu lisible). ; TPS/TVQ calculées à partir du total taxes incluses (126.45 $ = 109.98 HT + 5.50 TPS 5 % + 10.97 TVQ 9,975 %)</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>Amazon.ca</t>
+          <t>Amazon.ca (LLBA Professional)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -1884,43 +1884,39 @@
           <t>Matériel de cils</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
-        <is>
-          <t>702-3892259-3321860</t>
-        </is>
-      </c>
+      <c r="E18" s="23" t="inlineStr"/>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>Mouchoirs faciaux en velours Royale</t>
+          <t>Extensions de cils Curacoro</t>
         </is>
       </c>
       <c r="G18" s="24" t="n">
-        <v>34.99</v>
+        <v>16.06</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>1.75</v>
+        <v>0.8</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="J18" s="24" t="n">
-        <v>36.74</v>
+        <v>18.46</v>
       </c>
       <c r="K18" s="23" t="inlineStr">
         <is>
-          <t>PDF (lu par IA)</t>
+          <t>PDF (lu par IA), taxes calculées</t>
         </is>
       </c>
       <c r="L18" s="25" t="inlineStr">
         <is>
-          <t>TVQ imprimée à 0,00 $ sur le document; TPS 1,75 $.</t>
+          <t>Taxes incluses non détaillées. Date selon note manuscrite. ; TPS/TVQ calculées à partir du total taxes incluses (18.46 $ = 16.06 HT + 0.80 TPS 5 % + 1.60 TVQ 9,975 %)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
         </is>
       </c>
       <c r="B19" s="23" t="inlineStr">
@@ -1930,7 +1926,7 @@
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>Amazon.com.ca ULC</t>
+          <t>Amazon.ca</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -1940,12 +1936,12 @@
       </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
-          <t>CA82J18PMACCUI</t>
+          <t>702-3892259-3321860</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t>Royale Velour mouchoirs faciaux 24 boîtes</t>
+          <t>Mouchoirs faciaux en velours Royale</t>
         </is>
       </c>
       <c r="G19" s="24" t="n">
@@ -1967,7 +1963,7 @@
       </c>
       <c r="L19" s="25" t="inlineStr">
         <is>
-          <t>TVQ imprimée à 0,00 $</t>
+          <t>TVQ imprimée à 0,00 $ sur le document; TPS 1,75 $.</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1980,7 @@
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>Amazon.com.ca (qingdaoweimeishijiexinxikejiyouxiangongsi)</t>
+          <t>Amazon.com.ca ULC</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -1994,47 +1990,51 @@
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>CA899UIFFIII</t>
+          <t>CA82J18PMACCUI</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>VEYES INC extensions de cils volume classique</t>
+          <t>Royale Velour mouchoirs faciaux 24 boîtes</t>
         </is>
       </c>
       <c r="G20" s="24" t="n">
-        <v>11.79</v>
+        <v>34.99</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>0.59</v>
+        <v>1.75</v>
       </c>
       <c r="I20" s="24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="J20" s="24" t="n">
-        <v>13.56</v>
+        <v>36.74</v>
       </c>
       <c r="K20" s="23" t="inlineStr">
         <is>
           <t>PDF (lu par IA)</t>
         </is>
       </c>
-      <c r="L20" s="23" t="inlineStr"/>
+      <c r="L20" s="25" t="inlineStr">
+        <is>
+          <t>TVQ imprimée à 0,00 $</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
         </is>
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>Amazon.ca</t>
+          <t>Amazon.com.ca (qingdaoweimeishijiexinxikejiyouxiangongsi)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -2042,34 +2042,34 @@
           <t>Matériel de cils</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr"/>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>CA899UIFFIII</t>
+        </is>
+      </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t>Articles (2) – matériel de cils</t>
+          <t>VEYES INC extensions de cils volume classique</t>
         </is>
       </c>
       <c r="G21" s="24" t="n">
-        <v>27.53</v>
+        <v>11.79</v>
       </c>
       <c r="H21" s="24" t="n">
         <v>0.59</v>
       </c>
       <c r="I21" s="24" t="n">
-        <v>2.75</v>
+        <v>1.18</v>
       </c>
       <c r="J21" s="24" t="n">
-        <v>30.87</v>
+        <v>13.56</v>
       </c>
       <c r="K21" s="23" t="inlineStr">
         <is>
           <t>PDF (lu par IA)</t>
         </is>
       </c>
-      <c r="L21" s="25" t="inlineStr">
-        <is>
-          <t>HT = 32,78 $ − coupons 2,10 $ − promotion 3,15 $. Date selon note manuscrite/livraison.</t>
-        </is>
-      </c>
+      <c r="L21" s="23" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="23" t="inlineStr">
@@ -2079,47 +2079,47 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>La Perle Virtuelle</t>
+          <t>Amazon.ca</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>Soutien technique</t>
-        </is>
-      </c>
-      <c r="E22" s="23" t="inlineStr">
-        <is>
-          <t>26009</t>
-        </is>
-      </c>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr"/>
       <c r="F22" s="23" t="inlineStr">
         <is>
-          <t>Gestion opérationnelle – soutien technique et administratif</t>
+          <t>Articles (2) – matériel de cils</t>
         </is>
       </c>
       <c r="G22" s="24" t="n">
-        <v>1000</v>
+        <v>27.53</v>
       </c>
       <c r="H22" s="24" t="n">
-        <v>50</v>
+        <v>0.59</v>
       </c>
       <c r="I22" s="24" t="n">
-        <v>99.75</v>
+        <v>2.75</v>
       </c>
       <c r="J22" s="24" t="n">
-        <v>1149.75</v>
+        <v>30.87</v>
       </c>
       <c r="K22" s="23" t="inlineStr">
         <is>
           <t>PDF (lu par IA)</t>
         </is>
       </c>
-      <c r="L22" s="23" t="inlineStr"/>
+      <c r="L22" s="25" t="inlineStr">
+        <is>
+          <t>HT = 32,78 $ − coupons 2,10 $ − promotion 3,15 $. Date selon note manuscrite/livraison.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="23" t="inlineStr">
@@ -2129,51 +2129,47 @@
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>Amazon.ca</t>
+          <t>La Perle Virtuelle</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
         <is>
-          <t>Matériel de cils</t>
+          <t>Soutien technique</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
         <is>
-          <t>702-1576304-8553019</t>
+          <t>26009</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t>Poudre coréenne de cils PERMANIA + coussinets (lot)</t>
+          <t>Gestion opérationnelle – soutien technique et administratif</t>
         </is>
       </c>
       <c r="G23" s="24" t="n">
-        <v>45.97</v>
+        <v>1000</v>
       </c>
       <c r="H23" s="24" t="n">
-        <v>2.3</v>
+        <v>50</v>
       </c>
       <c r="I23" s="24" t="n">
-        <v>4.58</v>
+        <v>99.75</v>
       </c>
       <c r="J23" s="24" t="n">
-        <v>52.85</v>
+        <v>1149.75</v>
       </c>
       <c r="K23" s="23" t="inlineStr">
         <is>
           <t>PDF (lu par IA)</t>
         </is>
       </c>
-      <c r="L23" s="25" t="inlineStr">
-        <is>
-          <t>Même commande que la facture CA6G3SHGH4HI (page suivante) : risque de double comptage.</t>
-        </is>
-      </c>
+      <c r="L23" s="23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="23" t="inlineStr">
@@ -2183,12 +2179,12 @@
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>Amazon.ca (vendeur : putianshiqianmuhemaoyiyouxiangongsi)</t>
+          <t>Amazon.ca</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -2198,25 +2194,25 @@
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
-          <t>CA6G3SHGH4HI</t>
+          <t>702-1576304-8553019</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
         <is>
-          <t>Lash Lift Pads Kit, 3 paires (utuher)</t>
+          <t>Poudre coréenne de cils PERMANIA + coussinets (lot)</t>
         </is>
       </c>
       <c r="G24" s="24" t="n">
-        <v>9.99</v>
+        <v>45.97</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="I24" s="24" t="n">
-        <v>1</v>
+        <v>4.58</v>
       </c>
       <c r="J24" s="24" t="n">
-        <v>11.49</v>
+        <v>52.85</v>
       </c>
       <c r="K24" s="23" t="inlineStr">
         <is>
@@ -2225,7 +2221,7 @@
       </c>
       <c r="L24" s="25" t="inlineStr">
         <is>
-          <t>Facture partielle de la commande 702-1576304-8553019 (déjà incluse dans le total 52,85 $) : possible doublon.</t>
+          <t>Même commande que la facture CA6G3SHGH4HI (page suivante) : risque de double comptage.</t>
         </is>
       </c>
     </row>
@@ -2237,12 +2233,12 @@
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Amazon.ca (vendeur : putianshiqianmuhemaoyiyouxiangongsi)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -2250,49 +2246,53 @@
           <t>Matériel de cils</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr"/>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>CA6G3SHGH4HI</t>
+        </is>
+      </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t>Livraison Uber (Courier Saver)</t>
+          <t>Lash Lift Pads Kit, 3 paires (utuher)</t>
         </is>
       </c>
       <c r="G25" s="24" t="n">
-        <v>14.39</v>
+        <v>9.99</v>
       </c>
       <c r="H25" s="24" t="n">
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
       <c r="I25" s="24" t="n">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="J25" s="24" t="n">
-        <v>16.54</v>
+        <v>11.49</v>
       </c>
       <c r="K25" s="23" t="inlineStr">
         <is>
-          <t>PDF (lu par IA), taxes calculées</t>
+          <t>PDF (lu par IA)</t>
         </is>
       </c>
       <c r="L25" s="25" t="inlineStr">
         <is>
-          <t>Aucune taxe détaillée. ; TPS/TVQ calculées à partir du total taxes incluses (16.54 $ = 14.39 HT + 0.72 TPS 5 % + 1.43 TVQ 9,975 %)</t>
+          <t>Facture partielle de la commande 702-1576304-8553019 (déjà incluse dans le total 52,85 $) : possible doublon.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="23" t="inlineStr">
         <is>
-          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
         </is>
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>Amazon.ca (EXYGLO)</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -2300,53 +2300,49 @@
           <t>Matériel de cils</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
-        <is>
-          <t>702-0686830-7305820</t>
-        </is>
-      </c>
+      <c r="E26" s="23" t="inlineStr"/>
       <c r="F26" s="23" t="inlineStr">
         <is>
-          <t>Lot de 10 boîtes d'expédition (récapitulatif de commande)</t>
+          <t>Livraison Uber (Courier Saver)</t>
         </is>
       </c>
       <c r="G26" s="24" t="n">
-        <v>58.98</v>
+        <v>14.39</v>
       </c>
       <c r="H26" s="24" t="n">
-        <v>2.95</v>
+        <v>0.72</v>
       </c>
       <c r="I26" s="24" t="n">
-        <v>5.89</v>
+        <v>1.43</v>
       </c>
       <c r="J26" s="24" t="n">
-        <v>67.81999999999999</v>
+        <v>16.54</v>
       </c>
       <c r="K26" s="23" t="inlineStr">
         <is>
-          <t>PDF (lu par IA)</t>
+          <t>PDF (lu par IA), taxes calculées</t>
         </is>
       </c>
       <c r="L26" s="25" t="inlineStr">
         <is>
-          <t>Capture d'écran du récapitulatif de commande, numéro de commande utilisé comme numéro de facture</t>
+          <t>Aucune taxe détaillée. ; TPS/TVQ calculées à partir du total taxes incluses (16.54 $ = 14.39 HT + 0.72 TPS 5 % + 1.43 TVQ 9,975 %)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
         </is>
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>Amazon.ca</t>
+          <t>Amazon.ca (EXYGLO)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -2354,10 +2350,14 @@
           <t>Matériel de cils</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr"/>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>702-0686830-7305820</t>
+        </is>
+      </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t>Articles (2) – matériel de cils (dont boîtes d'expédition EXYGLO)</t>
+          <t>Lot de 10 boîtes d'expédition (récapitulatif de commande)</t>
         </is>
       </c>
       <c r="G27" s="24" t="n">
@@ -2379,24 +2379,24 @@
       </c>
       <c r="L27" s="25" t="inlineStr">
         <is>
-          <t>Date selon note manuscrite (livraison prévue 20 août).</t>
+          <t>Capture d'écran du récapitulatif de commande, numéro de commande utilisé comme numéro de facture</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="23" t="inlineStr">
         <is>
-          <t>2026-T3/IMG_2962.jpeg</t>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
         </is>
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>Canadian Tire #928</t>
+          <t>Amazon.ca</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -2404,53 +2404,49 @@
           <t>Matériel de cils</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
-        <is>
-          <t>TRANS 139</t>
-        </is>
-      </c>
+      <c r="E28" s="23" t="inlineStr"/>
       <c r="F28" s="23" t="inlineStr">
         <is>
-          <t>GLD BLEU P50 45 (article Canadian Tire)</t>
+          <t>Articles (2) – matériel de cils (dont boîtes d'expédition EXYGLO)</t>
         </is>
       </c>
       <c r="G28" s="24" t="n">
-        <v>13.99</v>
+        <v>58.98</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>0.7</v>
+        <v>2.95</v>
       </c>
       <c r="I28" s="24" t="n">
-        <v>1.4</v>
+        <v>5.89</v>
       </c>
       <c r="J28" s="24" t="n">
-        <v>16.09</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="K28" s="23" t="inlineStr">
         <is>
-          <t>photo (lue par IA)</t>
+          <t>PDF (lu par IA)</t>
         </is>
       </c>
       <c r="L28" s="25" t="inlineStr">
         <is>
-          <t>Annotation manuscrite « oct 2026 » ignorée. Date imprimée 08/25/2026.</t>
+          <t>Date selon note manuscrite (livraison prévue 20 août).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
+          <t>2026-T3/IMG_2962.jpeg</t>
         </is>
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
-          <t>Amazon.com.ca ULC</t>
+          <t>Canadian Tire #928</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
@@ -2460,32 +2456,36 @@
       </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
-          <t>CA62ZJ7TIACCUI</t>
+          <t>TRANS 139</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t>Ring Pop Candy 50 unités</t>
+          <t>GLD BLEU P50 45 (article Canadian Tire)</t>
         </is>
       </c>
       <c r="G29" s="24" t="n">
-        <v>31.15</v>
+        <v>13.99</v>
       </c>
       <c r="H29" s="24" t="n">
-        <v>1.56</v>
+        <v>0.7</v>
       </c>
       <c r="I29" s="24" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J29" s="24" t="n">
-        <v>35.81</v>
+        <v>16.09</v>
       </c>
       <c r="K29" s="23" t="inlineStr">
         <is>
-          <t>PDF (lu par IA)</t>
-        </is>
-      </c>
-      <c r="L29" s="23" t="inlineStr"/>
+          <t>photo (lue par IA)</t>
+        </is>
+      </c>
+      <c r="L29" s="25" t="inlineStr">
+        <is>
+          <t>Annotation manuscrite « oct 2026 » ignorée. Date imprimée 08/25/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="23" t="inlineStr">
@@ -2495,51 +2495,47 @@
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>Dollarama</t>
+          <t>Amazon.com.ca ULC</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>Frais de maintien divers</t>
+          <t>Matériel de cils</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>CA62ZJ7TIACCUI</t>
         </is>
       </c>
       <c r="F30" s="23" t="inlineStr">
         <is>
-          <t>Articles divers (Sherbrooke Est)</t>
+          <t>Ring Pop Candy 50 unités</t>
         </is>
       </c>
       <c r="G30" s="24" t="n">
-        <v>13.5</v>
+        <v>31.15</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>0.68</v>
+        <v>1.56</v>
       </c>
       <c r="I30" s="24" t="n">
-        <v>1.35</v>
+        <v>3.1</v>
       </c>
       <c r="J30" s="24" t="n">
-        <v>15.53</v>
+        <v>35.81</v>
       </c>
       <c r="K30" s="23" t="inlineStr">
         <is>
           <t>PDF (lu par IA)</t>
         </is>
       </c>
-      <c r="L30" s="25" t="inlineStr">
-        <is>
-          <t>Numéro de facture partiellement illisible</t>
-        </is>
-      </c>
+      <c r="L30" s="23" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="23" t="inlineStr">
@@ -2554,7 +2550,7 @@
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>Maxi &amp; Cie (Montréal Versailles)</t>
+          <t>Dollarama</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -2562,23 +2558,27 @@
           <t>Frais de maintien divers</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr"/>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>4318</t>
+        </is>
+      </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Articles divers (Sherbrooke Est)</t>
         </is>
       </c>
       <c r="G31" s="24" t="n">
-        <v>39.98</v>
+        <v>13.5</v>
       </c>
       <c r="H31" s="24" t="n">
-        <v>2</v>
+        <v>0.68</v>
       </c>
       <c r="I31" s="24" t="n">
-        <v>3.99</v>
+        <v>1.35</v>
       </c>
       <c r="J31" s="24" t="n">
-        <v>45.97</v>
+        <v>15.53</v>
       </c>
       <c r="K31" s="23" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="L31" s="25" t="inlineStr">
         <is>
-          <t>Reçu à l'envers; date 26/09/10; référence 142336</t>
+          <t>Numéro de facture partiellement illisible</t>
         </is>
       </c>
     </row>
@@ -2599,47 +2599,47 @@
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>La Perle Virtuelle</t>
+          <t>Maxi &amp; Cie (Montréal Versailles)</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>Soutien technique</t>
-        </is>
-      </c>
-      <c r="E32" s="23" t="inlineStr">
-        <is>
-          <t>26013</t>
-        </is>
-      </c>
+          <t>Frais de maintien divers</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr"/>
       <c r="F32" s="23" t="inlineStr">
         <is>
-          <t>Gestion opérationnelle - présence mensuelle</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="G32" s="24" t="n">
-        <v>500</v>
+        <v>39.98</v>
       </c>
       <c r="H32" s="24" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I32" s="24" t="n">
-        <v>49.87</v>
+        <v>3.99</v>
       </c>
       <c r="J32" s="24" t="n">
-        <v>574.88</v>
+        <v>45.97</v>
       </c>
       <c r="K32" s="23" t="inlineStr">
         <is>
           <t>PDF (lu par IA)</t>
         </is>
       </c>
-      <c r="L32" s="23" t="inlineStr"/>
+      <c r="L32" s="25" t="inlineStr">
+        <is>
+          <t>Reçu à l'envers; date 26/09/10; référence 142336</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="23" t="inlineStr">
@@ -2649,51 +2649,47 @@
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
         <is>
-          <t>DHL Express Canada Ltd</t>
+          <t>La Perle Virtuelle</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>Frais de livraison</t>
+          <t>Soutien technique</t>
         </is>
       </c>
       <c r="E33" s="23" t="inlineStr">
         <is>
-          <t>E103255297400</t>
+          <t>26013</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t>Droits et frais de dédouanement</t>
+          <t>Gestion opérationnelle - présence mensuelle</t>
         </is>
       </c>
       <c r="G33" s="24" t="n">
-        <v>30.93</v>
+        <v>500</v>
       </c>
       <c r="H33" s="24" t="n">
-        <v>7.16</v>
+        <v>25</v>
       </c>
       <c r="I33" s="24" t="n">
-        <v>0</v>
+        <v>49.87</v>
       </c>
       <c r="J33" s="24" t="n">
-        <v>38.09</v>
+        <v>574.88</v>
       </c>
       <c r="K33" s="23" t="inlineStr">
         <is>
           <t>PDF (lu par IA)</t>
         </is>
       </c>
-      <c r="L33" s="25" t="inlineStr">
-        <is>
-          <t>TPS sur importation 4,82 $ + TPS sur frais de dédouanement 2,34 $</t>
-        </is>
-      </c>
+      <c r="L33" s="23" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="23" t="inlineStr">
@@ -2703,47 +2699,51 @@
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
         <is>
-          <t>Amazon.com.ca (guangzhouxingyanshengwukejiyouxiangongsi)</t>
+          <t>DHL Express Canada Ltd</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
         <is>
-          <t>Matériel de cils</t>
+          <t>Frais de livraison</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
-          <t>CA63XQ7BDOQI</t>
+          <t>E103255297400</t>
         </is>
       </c>
       <c r="F34" s="23" t="inlineStr">
         <is>
-          <t>Trousse de rehaussement de cils ICONSIGN</t>
+          <t>Droits et frais de dédouanement</t>
         </is>
       </c>
       <c r="G34" s="24" t="n">
-        <v>16.99</v>
+        <v>30.93</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>0.85</v>
+        <v>7.16</v>
       </c>
       <c r="I34" s="24" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="J34" s="24" t="n">
-        <v>19.53</v>
+        <v>38.09</v>
       </c>
       <c r="K34" s="23" t="inlineStr">
         <is>
           <t>PDF (lu par IA)</t>
         </is>
       </c>
-      <c r="L34" s="23" t="inlineStr"/>
+      <c r="L34" s="25" t="inlineStr">
+        <is>
+          <t>TPS sur importation 4,82 $ + TPS sur frais de dédouanement 2,34 $</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="23" t="inlineStr">
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E35" s="23" t="inlineStr">
         <is>
-          <t>CA63XG7BDOOI</t>
+          <t>CA63XQ7BDOQI</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t>Fast Perm Lash Lift Kit</t>
+          <t>Trousse de rehaussement de cils ICONSIGN</t>
         </is>
       </c>
       <c r="G35" s="24" t="n">
@@ -2793,11 +2793,7 @@
           <t>PDF (lu par IA)</t>
         </is>
       </c>
-      <c r="L35" s="25" t="inlineStr">
-        <is>
-          <t>Même montant que la facture précédente mais numéro de facture et commande différents</t>
-        </is>
-      </c>
+      <c r="L35" s="23" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="23" t="inlineStr">
@@ -2807,12 +2803,12 @@
       </c>
       <c r="B36" s="23" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C36" s="23" t="inlineStr">
         <is>
-          <t>Amazon.com.ca (Shanghai Xijian Technology Co., Ltd)</t>
+          <t>Amazon.com.ca (guangzhouxingyanshengwukejiyouxiangongsi)</t>
         </is>
       </c>
       <c r="D36" s="23" t="inlineStr">
@@ -2822,25 +2818,25 @@
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>CA6GGKGO4C6I</t>
+          <t>CA63XG7BDOOI</t>
         </is>
       </c>
       <c r="F36" s="23" t="inlineStr">
         <is>
-          <t>Article ASIN B08BQXSRR7</t>
+          <t>Fast Perm Lash Lift Kit</t>
         </is>
       </c>
       <c r="G36" s="24" t="n">
-        <v>9.890000000000001</v>
+        <v>16.99</v>
       </c>
       <c r="H36" s="24" t="n">
-        <v>0.49</v>
+        <v>0.85</v>
       </c>
       <c r="I36" s="24" t="n">
-        <v>0.99</v>
+        <v>1.69</v>
       </c>
       <c r="J36" s="24" t="n">
-        <v>11.37</v>
+        <v>19.53</v>
       </c>
       <c r="K36" s="23" t="inlineStr">
         <is>
@@ -2849,7 +2845,7 @@
       </c>
       <c r="L36" s="25" t="inlineStr">
         <is>
-          <t>Prix 10,99 $ moins rabais 1,10 $</t>
+          <t>Même montant que la facture précédente mais numéro de facture et commande différents</t>
         </is>
       </c>
     </row>
@@ -2861,40 +2857,40 @@
       </c>
       <c r="B37" s="23" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C37" s="23" t="inlineStr">
         <is>
-          <t>DHL Express Canada Ltd</t>
+          <t>Amazon.com.ca (Shanghai Xijian Technology Co., Ltd)</t>
         </is>
       </c>
       <c r="D37" s="23" t="inlineStr">
         <is>
-          <t>Frais de livraison</t>
+          <t>Matériel de cils</t>
         </is>
       </c>
       <c r="E37" s="23" t="inlineStr">
         <is>
-          <t>E103278805700</t>
+          <t>CA6GGKGO4C6I</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t>Droits et frais de dédouanement</t>
+          <t>Article ASIN B08BQXSRR7</t>
         </is>
       </c>
       <c r="G37" s="24" t="n">
-        <v>76.06</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>23.97</v>
+        <v>0.49</v>
       </c>
       <c r="I37" s="24" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="J37" s="24" t="n">
-        <v>100.03</v>
+        <v>11.37</v>
       </c>
       <c r="K37" s="23" t="inlineStr">
         <is>
@@ -2903,7 +2899,7 @@
       </c>
       <c r="L37" s="25" t="inlineStr">
         <is>
-          <t>TPS sur importation 21,63 $ + TPS sur frais de dédouanement 2,34 $</t>
+          <t>Prix 10,99 $ moins rabais 1,10 $</t>
         </is>
       </c>
     </row>
@@ -2915,40 +2911,40 @@
       </c>
       <c r="B38" s="23" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C38" s="23" t="inlineStr">
         <is>
-          <t>Dollarama</t>
+          <t>DHL Express Canada Ltd</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
         <is>
-          <t>Frais de maintien divers</t>
+          <t>Frais de livraison</t>
         </is>
       </c>
       <c r="E38" s="23" t="inlineStr">
         <is>
-          <t>7942</t>
+          <t>E103278805700</t>
         </is>
       </c>
       <c r="F38" s="23" t="inlineStr">
         <is>
-          <t>Effaces magiques et cadres document</t>
+          <t>Droits et frais de dédouanement</t>
         </is>
       </c>
       <c r="G38" s="24" t="n">
-        <v>14.5</v>
+        <v>76.06</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>0.73</v>
+        <v>23.97</v>
       </c>
       <c r="I38" s="24" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="J38" s="24" t="n">
-        <v>16.68</v>
+        <v>100.03</v>
       </c>
       <c r="K38" s="23" t="inlineStr">
         <is>
@@ -2957,103 +2953,111 @@
       </c>
       <c r="L38" s="25" t="inlineStr">
         <is>
-          <t>Date 2026-10-04 hors du trimestre 2026-T3</t>
+          <t>TPS sur importation 21,63 $ + TPS sur frais de dédouanement 2,34 $</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="23" t="inlineStr">
         <is>
-          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
-        </is>
-      </c>
-      <c r="B39" s="23" t="n"/>
+          <t>2026-T3/Dépenses_T3-21-39.pdf</t>
+        </is>
+      </c>
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
       <c r="C39" s="23" t="inlineStr">
         <is>
-          <t>Fournisseur non indiqué (commande en ligne, livraison à Montréal)</t>
+          <t>Dollarama</t>
         </is>
       </c>
       <c r="D39" s="23" t="inlineStr">
         <is>
-          <t>Matériel de cils</t>
-        </is>
-      </c>
-      <c r="E39" s="23" t="inlineStr"/>
+          <t>Frais de maintien divers</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
+        <is>
+          <t>7942</t>
+        </is>
+      </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t>Marchandise et expédition</t>
+          <t>Effaces magiques et cadres document</t>
         </is>
       </c>
       <c r="G39" s="24" t="n">
-        <v>517.28</v>
+        <v>14.5</v>
       </c>
       <c r="H39" s="24" t="n">
-        <v>25.86</v>
+        <v>0.73</v>
       </c>
       <c r="I39" s="24" t="n">
-        <v>51.6</v>
+        <v>1.45</v>
       </c>
       <c r="J39" s="24" t="n">
-        <v>594.74</v>
+        <v>16.68</v>
       </c>
       <c r="K39" s="23" t="inlineStr">
         <is>
-          <t>PDF (lu par IA), taxe combinée répartie</t>
+          <t>PDF (lu par IA)</t>
         </is>
       </c>
       <c r="L39" s="25" t="inlineStr">
         <is>
-          <t>Fournisseur et date non visibles. Sous-total 507,29 $ + expédition 9,99 $. Taxes de vente combinées 77,46 $. ; TPS/TVQ réparties à partir de la taxe combinée imprimée (77.46 $ = 25.86 TPS 5 % + 51.60 TVQ 9,975 %)</t>
+          <t>Date 2026-10-04 hors du trimestre 2026-T3 ; Date 2026-10-04 hors du trimestre 2026-T3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="23" t="inlineStr">
         <is>
-          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
-        </is>
-      </c>
-      <c r="B40" s="23" t="n"/>
+          <t>2026-T3/Telus.jpeg</t>
+        </is>
+      </c>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="C40" s="23" t="inlineStr">
         <is>
-          <t>NovoQueen Pro</t>
+          <t>TELUS Mobilité</t>
         </is>
       </c>
       <c r="D40" s="23" t="inlineStr">
         <is>
-          <t>Matériel de cils</t>
-        </is>
-      </c>
-      <c r="E40" s="23" t="inlineStr">
-        <is>
-          <t>MF04A537Y</t>
-        </is>
-      </c>
+          <t>Frais Téléphonie et Prêt</t>
+        </is>
+      </c>
+      <c r="E40" s="23" t="inlineStr"/>
       <c r="F40" s="23" t="inlineStr">
         <is>
-          <t>L'expérience Glow &amp; Grow 2027 (formation)</t>
+          <t>Services mobiles TELUS (période sept. 2026)</t>
         </is>
       </c>
       <c r="G40" s="24" t="n">
-        <v>555</v>
+        <v>537.3</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>27.75</v>
+        <v>26.88</v>
       </c>
       <c r="I40" s="24" t="n">
-        <v>55.36</v>
+        <v>53.61</v>
       </c>
       <c r="J40" s="24" t="n">
-        <v>638.11</v>
+        <v>617.79</v>
       </c>
       <c r="K40" s="23" t="inlineStr">
         <is>
-          <t>PDF (lu par IA), taxe combinée répartie</t>
+          <t>photo (lue par IA), taxe combinée répartie, × 3 mois</t>
         </is>
       </c>
       <c r="L40" s="25" t="inlineStr">
         <is>
-          <t>Taxes estimées combinées 83,11 $. Date non visible. ; TPS/TVQ réparties à partir de la taxe combinée imprimée (83.11 $ = 27.75 TPS 5 % + 55.36 TVQ 9,975 %)</t>
+          <t>Taxes combinées de 26,83 $ imprimées sans distinction TPS/TVQ (annotation manuscrite « ? TPS / ? TVQ »). Numéro de compte 40892992. Économies de 20,00 $ ce mois-ci déjà reflétées dans les frais. ; TPS/TVQ réparties à partir de la taxe combinée imprimée (26.83 $ = 8.96 TPS 5 % + 17.87 TVQ 9,975 %) ; Date 2026-10-13 hors du trimestre 2026-T3 ; Facture Telus mensuelle × 3 (même montant payé chaque mois du trimestre)</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3070,7 @@
       <c r="B41" s="23" t="n"/>
       <c r="C41" s="23" t="inlineStr">
         <is>
-          <t>Temu (présumé, application d'achat en ligne)</t>
+          <t>Fournisseur non indiqué (commande en ligne, livraison à Montréal)</t>
         </is>
       </c>
       <c r="D41" s="23" t="inlineStr">
@@ -3077,29 +3081,29 @@
       <c r="E41" s="23" t="inlineStr"/>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t>Commande de 20 articles (brosses à cils, etc.)</t>
+          <t>Marchandise et expédition</t>
         </is>
       </c>
       <c r="G41" s="24" t="n">
-        <v>249.4</v>
+        <v>517.28</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>12.46</v>
+        <v>25.86</v>
       </c>
       <c r="I41" s="24" t="n">
-        <v>24.88</v>
+        <v>51.6</v>
       </c>
       <c r="J41" s="24" t="n">
-        <v>286.74</v>
+        <v>594.74</v>
       </c>
       <c r="K41" s="23" t="inlineStr">
         <is>
-          <t>PDF (lu par IA)</t>
+          <t>PDF (lu par IA), taxe combinée répartie</t>
         </is>
       </c>
       <c r="L41" s="25" t="inlineStr">
         <is>
-          <t>Taxes incluses détaillées (GST 12,46 $ / QST 24,88 $; total 37,34 $). HT calculé = total − taxes. Fournisseur et date non visibles.</t>
+          <t>Fournisseur et date non visibles. Sous-total 507,29 $ + expédition 9,99 $. Taxes de vente combinées 77,46 $. ; TPS/TVQ réparties à partir de la taxe combinée imprimée (77.46 $ = 25.86 TPS 5 % + 51.60 TVQ 9,975 %)</t>
         </is>
       </c>
     </row>
@@ -3112,44 +3116,44 @@
       <c r="B42" s="23" t="n"/>
       <c r="C42" s="23" t="inlineStr">
         <is>
-          <t>ZAHKA SNC</t>
+          <t>NovoQueen Pro</t>
         </is>
       </c>
       <c r="D42" s="23" t="inlineStr">
         <is>
-          <t>Service d'accompagnement en ligne de marque</t>
+          <t>Matériel de cils</t>
         </is>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>MF04A537Y</t>
         </is>
       </c>
       <c r="F42" s="23" t="inlineStr">
         <is>
-          <t>Service d'accompagnement en image de marque</t>
+          <t>L'expérience Glow &amp; Grow 2027 (formation)</t>
         </is>
       </c>
       <c r="G42" s="24" t="n">
-        <v>400</v>
+        <v>555</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>20</v>
+        <v>27.75</v>
       </c>
       <c r="I42" s="24" t="n">
-        <v>39.9</v>
+        <v>55.36</v>
       </c>
       <c r="J42" s="24" t="n">
-        <v>459.9</v>
+        <v>638.11</v>
       </c>
       <c r="K42" s="23" t="inlineStr">
         <is>
-          <t>PDF (lu par IA)</t>
+          <t>PDF (lu par IA), taxe combinée répartie</t>
         </is>
       </c>
       <c r="L42" s="25" t="inlineStr">
         <is>
-          <t>Date non imprimée (août 2026 selon note manuscrite).</t>
+          <t>Taxes estimées combinées 83,11 $. Date non visible. ; TPS/TVQ réparties à partir de la taxe combinée imprimée (83.11 $ = 27.75 TPS 5 % + 55.36 TVQ 9,975 %)</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3166,7 @@
       <c r="B43" s="23" t="n"/>
       <c r="C43" s="23" t="inlineStr">
         <is>
-          <t>Muhammad Adnan Muhammad Aslam (virement)</t>
+          <t>Temu (présumé, application d'achat en ligne)</t>
         </is>
       </c>
       <c r="D43" s="23" t="inlineStr">
@@ -3173,55 +3177,151 @@
       <c r="E43" s="23" t="inlineStr"/>
       <c r="F43" s="23" t="inlineStr">
         <is>
+          <t>Commande de 20 articles (brosses à cils, etc.)</t>
+        </is>
+      </c>
+      <c r="G43" s="24" t="n">
+        <v>249.4</v>
+      </c>
+      <c r="H43" s="24" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="I43" s="24" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="J43" s="24" t="n">
+        <v>286.74</v>
+      </c>
+      <c r="K43" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L43" s="25" t="inlineStr">
+        <is>
+          <t>Taxes incluses détaillées (GST 12,46 $ / QST 24,88 $; total 37,34 $). HT calculé = total − taxes. Fournisseur et date non visibles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+        </is>
+      </c>
+      <c r="B44" s="23" t="n"/>
+      <c r="C44" s="23" t="inlineStr">
+        <is>
+          <t>ZAHKA SNC</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="inlineStr">
+        <is>
+          <t>Service d'accompagnement en ligne de marque</t>
+        </is>
+      </c>
+      <c r="E44" s="23" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="inlineStr">
+        <is>
+          <t>Service d'accompagnement en image de marque</t>
+        </is>
+      </c>
+      <c r="G44" s="24" t="n">
+        <v>400</v>
+      </c>
+      <c r="H44" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="I44" s="24" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="J44" s="24" t="n">
+        <v>459.9</v>
+      </c>
+      <c r="K44" s="23" t="inlineStr">
+        <is>
+          <t>PDF (lu par IA)</t>
+        </is>
+      </c>
+      <c r="L44" s="25" t="inlineStr">
+        <is>
+          <t>Date non imprimée (août 2026 selon note manuscrite).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="23" t="inlineStr">
+        <is>
+          <t>2026-T3/Dépenses_T3-1-20.pdf</t>
+        </is>
+      </c>
+      <c r="B45" s="23" t="n"/>
+      <c r="C45" s="23" t="inlineStr">
+        <is>
+          <t>Muhammad Adnan Muhammad Aslam (virement)</t>
+        </is>
+      </c>
+      <c r="D45" s="23" t="inlineStr">
+        <is>
+          <t>Matériel de cils</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="inlineStr"/>
+      <c r="F45" s="23" t="inlineStr">
+        <is>
           <t>Pinces à cils (virement)</t>
         </is>
       </c>
-      <c r="G43" s="24" t="n">
+      <c r="G45" s="24" t="n">
         <v>375.76</v>
       </c>
-      <c r="H43" s="24" t="n">
+      <c r="H45" s="24" t="n">
         <v>18.79</v>
       </c>
-      <c r="I43" s="24" t="n">
+      <c r="I45" s="24" t="n">
         <v>37.48</v>
       </c>
-      <c r="J43" s="24" t="n">
+      <c r="J45" s="24" t="n">
         <v>432.03</v>
       </c>
-      <c r="K43" s="23" t="inlineStr">
+      <c r="K45" s="23" t="inlineStr">
         <is>
           <t>PDF (lu par IA), taxes calculées</t>
         </is>
       </c>
-      <c r="L43" s="25" t="inlineStr">
+      <c r="L45" s="25" t="inlineStr">
         <is>
           <t>Confirmation de virement seulement, aucune taxe imprimée; date non visible (août 2026 selon note manuscrite). ; TPS/TVQ calculées à partir du total taxes incluses (432.03 $ = 375.76 HT + 18.79 TPS 5 % + 37.48 TVQ 9,975 %)</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="26" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="26" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B44" s="26" t="n"/>
-      <c r="C44" s="26" t="n"/>
-      <c r="D44" s="26" t="n"/>
-      <c r="E44" s="26" t="n"/>
-      <c r="F44" s="26" t="n"/>
-      <c r="G44" s="27" t="n">
-        <v>5577.05</v>
-      </c>
-      <c r="H44" s="27" t="n">
-        <v>303.61</v>
-      </c>
-      <c r="I44" s="27" t="n">
-        <v>538.1799999999999</v>
-      </c>
-      <c r="J44" s="26" t="n"/>
-      <c r="K44" s="26" t="n"/>
-      <c r="L44" s="26" t="n"/>
+      <c r="B46" s="26" t="n"/>
+      <c r="C46" s="26" t="n"/>
+      <c r="D46" s="26" t="n"/>
+      <c r="E46" s="26" t="n"/>
+      <c r="F46" s="26" t="n"/>
+      <c r="G46" s="27" t="n">
+        <v>7863.35</v>
+      </c>
+      <c r="H46" s="27" t="n">
+        <v>417.94</v>
+      </c>
+      <c r="I46" s="27" t="n">
+        <v>766.25</v>
+      </c>
+      <c r="J46" s="26" t="n"/>
+      <c r="K46" s="26" t="n"/>
+      <c r="L46" s="26" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/orders/2026-T3_declaration_tps_tvq.xlsx
+++ b/data/orders/2026-T3_declaration_tps_tvq.xlsx
@@ -1369,7 +1369,7 @@
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t>Matériel de cils</t>
+          <t>Frais Téléphonie et Prêt</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="L8" s="25" t="inlineStr">
         <is>
-          <t>Impôts/taxes de 261,91 $ imprimés sans distinction TPS/TVQ (à calculer, repère « ? » de l'entreprise). Prêt de 1 749,00 $ (72,88 $/mois x 24). Total = prêt + taxes (calculé). Date non imprimée : période juillet 2026 selon la note manuscrite. ; TPS/TVQ réparties à partir de la taxe combinée imprimée (261.91 $ = 87.45 TPS 5 % + 174.46 TVQ 9,975 %)</t>
+          <t>Impôts/taxes de 261,91 $ imprimés sans distinction TPS/TVQ (à calculer, repère « ? » de l'entreprise). Prêt de 1 749,00 $ (72,88 $/mois x 24). Total = prêt + taxes (calculé). Date non imprimée : période juillet 2026 selon la note manuscrite. ; TPS/TVQ réparties à partir de la taxe combinée imprimée (261.91 $ = 87.45 TPS 5 % + 174.46 TVQ 9,975 %) ; Prêt téléphone Telus : taxe payée une seule fois, comptée telle quelle (pas de × 3)</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="L40" s="25" t="inlineStr">
         <is>
-          <t>Taxes combinées de 26,83 $ imprimées sans distinction TPS/TVQ (annotation manuscrite « ? TPS / ? TVQ »). Numéro de compte 40892992. Économies de 20,00 $ ce mois-ci déjà reflétées dans les frais. ; TPS/TVQ réparties à partir de la taxe combinée imprimée (26.83 $ = 8.96 TPS 5 % + 17.87 TVQ 9,975 %) ; Date 2026-10-13 hors du trimestre 2026-T3 ; Facture Telus mensuelle × 3 (même montant payé chaque mois du trimestre)</t>
+          <t>Taxes combinées de 26,83 $ imprimées sans distinction TPS/TVQ (annotation manuscrite « ? TPS / ? TVQ »). Numéro de compte 40892992. Économies de 20,00 $ ce mois-ci déjà reflétées dans les frais. ; TPS/TVQ réparties à partir de la taxe combinée imprimée (26.83 $ = 8.96 TPS 5 % + 17.87 TVQ 9,975 %) ; Date 2026-10-13 hors du trimestre 2026-T3 ; Date 2026-10-13 hors du trimestre 2026-T3 ; Facture Telus mensuelle × 3 (même montant payé chaque mois du trimestre)</t>
         </is>
       </c>
     </row>
